--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/565755648f0a3f81/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{331269C5-3CF7-434D-8E0B-4BD1E60EDCCD}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D16B17EC-B6FE-4610-8EF2-9AD3F8BEBA7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1537,21 +1537,27 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1060</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/565755648f0a3f81/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D16B17EC-B6FE-4610-8EF2-9AD3F8BEBA7D}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4211C083-36D5-4EF3-9AD8-64781759248A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -431,9 +431,9 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,74 +917,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12602441</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="45">
       <c r="A5" s="7" t="s">
@@ -1546,45 +1546,87 @@
       <c r="C17" s="14">
         <v>20</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>150</v>
+      </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>1070</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>1060</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>350</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>150</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/565755648f0a3f81/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4211C083-36D5-4EF3-9AD8-64781759248A}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="8_{F92E2664-E68F-4788-901C-B0B3E7C55010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD9633C5-BBAE-4FD2-9DE1-6F81347C3148}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1629,26 +1629,50 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>140</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -29,6 +32,9 @@
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t>2. WHERE TO ENTER DATA</t>
   </si>
   <si>
@@ -39,6 +45,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
@@ -95,6 +104,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -102,18 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
-  </si>
-  <si>
-    <t>Name:</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -236,6 +236,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -258,12 +264,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -277,7 +277,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -439,6 +438,9 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -449,9 +451,6 @@
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +688,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="105.0"/>
-    <col customWidth="1" min="2" max="26" width="8.57"/>
+    <col customWidth="1" min="2" max="6" width="8.57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,176 +697,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
+      <c r="A6" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
+      <c r="A9" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
+      <c r="A10" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
+      <c r="A11" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
+      <c r="A13" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>10</v>
+      <c r="A14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
+      <c r="A15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>12</v>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>13</v>
+      <c r="A18" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>14</v>
+      <c r="A19" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>15</v>
+      <c r="A20" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>16</v>
+      <c r="A21" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>17</v>
+      <c r="A22" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>18</v>
+      <c r="A23" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
+      <c r="A24" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>20</v>
+      <c r="A25" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
+      <c r="A26" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>22</v>
+      <c r="A27" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>23</v>
+      <c r="A28" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
+      <c r="A29" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>25</v>
+      <c r="A30" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>26</v>
+      <c r="A31" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>27</v>
+      <c r="A33" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>28</v>
+      <c r="A34" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>29</v>
+      <c r="A35" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1854,33 +1853,32 @@
     <col customWidth="1" min="12" max="12" width="15.0"/>
     <col customWidth="1" min="13" max="13" width="12.0"/>
     <col customWidth="1" min="14" max="14" width="28.0"/>
-    <col customWidth="1" min="15" max="26" width="8.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>30</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
       </c>
       <c r="G2" s="10"/>
       <c r="M2" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Fill an appropriate value for this cell based on the table context"")"),"")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Fill an appropriate value for this cell based on the table context"")"),"=AI(""Fill an appropriate value for this cell based on the table context"")")</f>
+        <v>=AI("Fill an appropriate value for this cell based on the table context")</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -2643,25 +2641,25 @@
       <c r="A21" s="26">
         <v>46269.0</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="20">
         <v>360.0</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="20">
         <v>25.0</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="20">
         <v>150.0</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="20">
         <v>100.0</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="20">
         <v>250.0</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="20">
         <v>5.0</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="20">
         <v>180.0</v>
       </c>
       <c r="I21" s="21">
@@ -2672,42 +2670,42 @@
         <f t="shared" si="2"/>
         <v>375</v>
       </c>
-      <c r="K21" s="28" t="s">
+      <c r="K21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="28" t="s">
+      <c r="M21" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="29" t="s">
+      <c r="N21" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="30">
+      <c r="A22" s="19">
         <v>46270.0</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="20">
         <v>360.0</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="20">
         <v>20.0</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="20">
         <v>150.0</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="20">
         <v>180.0</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="20">
         <v>0.0</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="20">
         <v>0.0</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="20">
         <v>140.0</v>
       </c>
       <c r="I22" s="21">
@@ -2718,42 +2716,42 @@
         <f t="shared" si="2"/>
         <v>590</v>
       </c>
-      <c r="K22" s="28" t="s">
+      <c r="K22" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="28" t="s">
+      <c r="M22" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="N22" s="29" t="s">
+      <c r="N22" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="30">
+      <c r="A23" s="19">
         <v>46271.0</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="20">
         <v>420.0</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="20">
         <v>20.0</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="20">
         <v>140.0</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="20">
         <v>200.0</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="20">
         <v>0.0</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="20">
         <v>0.0</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="20">
         <v>180.0</v>
       </c>
       <c r="I23" s="21">
@@ -2764,42 +2762,42 @@
         <f t="shared" si="2"/>
         <v>480</v>
       </c>
-      <c r="K23" s="28" t="s">
+      <c r="K23" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L23" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="29" t="s">
+      <c r="N23" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="30">
+      <c r="A24" s="19">
         <v>46272.0</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="20">
         <v>360.0</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="20">
         <v>30.0</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="20">
         <v>100.0</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="20">
         <v>120.0</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="20">
         <v>250.0</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="20">
         <v>5.0</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="20">
         <v>150.0</v>
       </c>
       <c r="I24" s="21">
@@ -2810,40 +2808,64 @@
         <f t="shared" si="2"/>
         <v>430</v>
       </c>
-      <c r="K24" s="28" t="s">
+      <c r="K24" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N24" s="29" t="s">
+      <c r="N24" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="23"/>
+      <c r="A25" s="27">
+        <v>46273.0</v>
+      </c>
+      <c r="B25" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C25" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="D25" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E25" s="28">
+        <v>110.0</v>
+      </c>
+      <c r="F25" s="28">
+        <v>350.0</v>
+      </c>
+      <c r="G25" s="28">
+        <v>7.0</v>
+      </c>
+      <c r="H25" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="1"/>
+        <v>1090</v>
+      </c>
+      <c r="J25" s="21">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="K25" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,18 +12,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
-    <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
@@ -86,6 +86,9 @@
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
   </si>
   <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
@@ -102,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
@@ -236,12 +236,6 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -254,6 +248,12 @@
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -697,17 +697,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
@@ -715,12 +715,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
@@ -728,40 +728,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
+      <c r="A12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
@@ -769,77 +769,77 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>24</v>
+      <c r="A26" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>25</v>
+      <c r="A27" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>26</v>
+      <c r="A28" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>27</v>
+      <c r="A29" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>28</v>
+      <c r="A30" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>29</v>
+      <c r="A31" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
+      <c r="A32" s="4"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
@@ -847,26 +847,26 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1856,8 +1856,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
@@ -1865,12 +1865,12 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -2822,28 +2822,28 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="27">
+      <c r="A25" s="19">
         <v>46273.0</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="20">
         <v>360.0</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="20">
         <v>20.0</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="20">
         <v>100.0</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="20">
         <v>110.0</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="20">
         <v>350.0</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="20">
         <v>7.0</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="20">
         <v>150.0</v>
       </c>
       <c r="I25" s="21">
@@ -2854,40 +2854,64 @@
         <f t="shared" si="2"/>
         <v>350</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="29" t="s">
+      <c r="L25" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M25" s="29" t="s">
+      <c r="M25" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="30" t="s">
+      <c r="N25" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="23"/>
+      <c r="A26" s="27">
+        <v>46274.0</v>
+      </c>
+      <c r="B26" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C26" s="28">
+        <v>25.0</v>
+      </c>
+      <c r="D26" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E26" s="28">
+        <v>140.0</v>
+      </c>
+      <c r="F26" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="G26" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="H26" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I26" s="21">
+        <f t="shared" si="1"/>
+        <v>1075</v>
+      </c>
+      <c r="J26" s="21">
+        <f t="shared" si="2"/>
+        <v>365</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -23,16 +26,16 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>Name:</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -50,7 +53,7 @@
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
@@ -86,9 +89,6 @@
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
@@ -101,7 +101,13 @@
     <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
+  </si>
+  <si>
+    <t>MCA</t>
   </si>
   <si>
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
@@ -113,19 +119,13 @@
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
     <t>Month:</t>
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -236,6 +236,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -246,26 +252,20 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -697,176 +697,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
+      <c r="A5" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
+      <c r="A6" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
+      <c r="A8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
+      <c r="A10" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>11</v>
+      <c r="A13" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>13</v>
+      <c r="A14" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
+      <c r="A15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>15</v>
+      <c r="A17" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>16</v>
+      <c r="A18" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>17</v>
+      <c r="A19" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>18</v>
+      <c r="A20" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>19</v>
+      <c r="A21" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
+      <c r="A22" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>21</v>
+      <c r="A23" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>22</v>
+      <c r="A24" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>23</v>
+      <c r="A25" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>29</v>
+      <c r="A30" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>30</v>
+      <c r="A31" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>31</v>
+      <c r="A33" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>32</v>
+      <c r="A34" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>33</v>
+      <c r="A35" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1856,21 +1856,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>3</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>24</v>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1882,19 +1882,19 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>34</v>
+      <c r="A3" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -2868,28 +2868,28 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="27">
+      <c r="A26" s="19">
         <v>46274.0</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="20">
         <v>360.0</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="20">
         <v>25.0</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="20">
         <v>100.0</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="20">
         <v>140.0</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="20">
         <v>300.0</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="20">
         <v>6.0</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="20">
         <v>150.0</v>
       </c>
       <c r="I26" s="21">
@@ -2900,40 +2900,64 @@
         <f t="shared" si="2"/>
         <v>365</v>
       </c>
-      <c r="K26" s="29" t="s">
+      <c r="K26" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="L26" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="29" t="s">
+      <c r="M26" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N26" s="30" t="s">
+      <c r="N26" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="19"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="23"/>
+      <c r="A27" s="27">
+        <v>46275.0</v>
+      </c>
+      <c r="B27" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C27" s="28">
+        <v>25.0</v>
+      </c>
+      <c r="D27" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E27" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="F27" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="G27" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="H27" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="1"/>
+        <v>935</v>
+      </c>
+      <c r="J27" s="21">
+        <f t="shared" si="2"/>
+        <v>505</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -32,10 +32,10 @@
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -53,13 +53,13 @@
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
   </si>
   <si>
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t>4. COLUMN GUIDE</t>
@@ -101,13 +101,7 @@
     <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
   </si>
   <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
-  </si>
-  <si>
-    <t>MCA</t>
   </si>
   <si>
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
@@ -119,13 +113,19 @@
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t>Month:</t>
   </si>
   <si>
     <t>August</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -236,13 +236,13 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF595959"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -252,13 +252,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <b/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -697,7 +697,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
@@ -715,12 +715,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
+      <c r="A6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
@@ -728,22 +728,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
@@ -751,17 +751,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="6"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
@@ -769,104 +769,104 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1856,21 +1856,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
+      <c r="E2" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1882,19 +1882,19 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>29</v>
+      <c r="A3" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
+      <c r="E3" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -1973,11 +1973,11 @@
         <v>30.0</v>
       </c>
       <c r="I6" s="16">
-        <f t="shared" ref="I6:I401" si="1">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I18" si="1">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="16">
-        <f t="shared" ref="J6:J401" si="2">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J18" si="2">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="17" t="s">
@@ -2570,13 +2570,10 @@
       <c r="H19" s="20">
         <v>140.0</v>
       </c>
-      <c r="I19" s="21">
-        <f t="shared" si="1"/>
-        <v>1060</v>
-      </c>
-      <c r="J19" s="21">
-        <f t="shared" si="2"/>
-        <v>380</v>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="str">
+        <f>IF(#REF!="","",1440-#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>53</v>
@@ -2617,11 +2614,11 @@
         <v>180.0</v>
       </c>
       <c r="I20" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I20:I401" si="3">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
         <v>940</v>
       </c>
       <c r="J20" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J20:J401" si="4">IF(I20="","",1440-I20)</f>
         <v>500</v>
       </c>
       <c r="K20" s="22" t="s">
@@ -2663,11 +2660,11 @@
         <v>180.0</v>
       </c>
       <c r="I21" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1065</v>
       </c>
       <c r="J21" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>375</v>
       </c>
       <c r="K21" s="22" t="s">
@@ -2709,11 +2706,11 @@
         <v>140.0</v>
       </c>
       <c r="I22" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>850</v>
       </c>
       <c r="J22" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>590</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -2755,11 +2752,11 @@
         <v>180.0</v>
       </c>
       <c r="I23" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>960</v>
       </c>
       <c r="J23" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="K23" s="22" t="s">
@@ -2801,11 +2798,11 @@
         <v>150.0</v>
       </c>
       <c r="I24" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1010</v>
       </c>
       <c r="J24" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="K24" s="22" t="s">
@@ -2847,11 +2844,11 @@
         <v>150.0</v>
       </c>
       <c r="I25" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1090</v>
       </c>
       <c r="J25" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>350</v>
       </c>
       <c r="K25" s="22" t="s">
@@ -2893,11 +2890,11 @@
         <v>150.0</v>
       </c>
       <c r="I26" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1075</v>
       </c>
       <c r="J26" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>365</v>
       </c>
       <c r="K26" s="22" t="s">
@@ -2914,94 +2911,142 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="27">
+      <c r="A27" s="19">
         <v>46275.0</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="20">
         <v>360.0</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="20">
         <v>25.0</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="20">
         <v>100.0</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="20">
         <v>150.0</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="20">
         <v>100.0</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="20">
         <v>2.0</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="20">
         <v>200.0</v>
       </c>
       <c r="I27" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>935</v>
       </c>
       <c r="J27" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>505</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L27" s="29" t="s">
+      <c r="L27" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M27" s="29" t="s">
+      <c r="M27" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="30" t="s">
+      <c r="N27" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J28" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="23"/>
+      <c r="A28" s="27">
+        <v>46276.0</v>
+      </c>
+      <c r="B28" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C28" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="D28" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="E28" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="F28" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="G28" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="H28" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I28" s="21">
+        <f t="shared" si="3"/>
+        <v>1050</v>
+      </c>
+      <c r="J28" s="21">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="23"/>
+      <c r="A29" s="27">
+        <v>46277.0</v>
+      </c>
+      <c r="B29" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C29" s="28">
+        <v>25.0</v>
+      </c>
+      <c r="D29" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E29" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="F29" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I29" s="21">
+        <f t="shared" si="3"/>
+        <v>785</v>
+      </c>
+      <c r="J29" s="21">
+        <f t="shared" si="4"/>
+        <v>655</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N29" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="19"/>
@@ -3013,17 +3058,16 @@
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="I30" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J30" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
-      <c r="N30" s="23"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19"/>
@@ -3035,11 +3079,11 @@
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="I31" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J31" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K31" s="22"/>
@@ -3057,11 +3101,11 @@
       <c r="G32" s="20"/>
       <c r="H32" s="20"/>
       <c r="I32" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J32" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K32" s="22"/>
@@ -3079,11 +3123,11 @@
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
       <c r="I33" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J33" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K33" s="22"/>
@@ -3101,11 +3145,11 @@
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
       <c r="I34" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J34" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K34" s="22"/>
@@ -3123,11 +3167,11 @@
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
       <c r="I35" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J35" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K35" s="22"/>
@@ -3145,11 +3189,11 @@
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
       <c r="I36" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J36" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K36" s="22"/>
@@ -3167,11 +3211,11 @@
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
       <c r="I37" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J37" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K37" s="22"/>
@@ -3189,11 +3233,11 @@
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
       <c r="I38" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J38" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K38" s="22"/>
@@ -3211,11 +3255,11 @@
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
       <c r="I39" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J39" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K39" s="22"/>
@@ -3233,11 +3277,11 @@
       <c r="G40" s="20"/>
       <c r="H40" s="20"/>
       <c r="I40" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J40" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K40" s="22"/>
@@ -3255,11 +3299,11 @@
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
       <c r="I41" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J41" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K41" s="22"/>
@@ -3277,11 +3321,11 @@
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
       <c r="I42" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J42" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K42" s="22"/>
@@ -3299,11 +3343,11 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
       <c r="I43" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J43" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K43" s="22"/>
@@ -3321,11 +3365,11 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
       <c r="I44" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J44" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K44" s="22"/>
@@ -3343,11 +3387,11 @@
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
       <c r="I45" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J45" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K45" s="22"/>
@@ -3365,11 +3409,11 @@
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
       <c r="I46" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J46" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K46" s="22"/>
@@ -3387,11 +3431,11 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
       <c r="I47" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J47" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K47" s="22"/>
@@ -3409,11 +3453,11 @@
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
       <c r="I48" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J48" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K48" s="22"/>
@@ -3431,11 +3475,11 @@
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
       <c r="I49" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J49" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K49" s="22"/>
@@ -3453,11 +3497,11 @@
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
       <c r="I50" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J50" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K50" s="22"/>
@@ -3475,11 +3519,11 @@
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
       <c r="I51" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J51" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K51" s="22"/>
@@ -3497,11 +3541,11 @@
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
       <c r="I52" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J52" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K52" s="22"/>
@@ -3519,11 +3563,11 @@
       <c r="G53" s="20"/>
       <c r="H53" s="20"/>
       <c r="I53" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J53" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K53" s="22"/>
@@ -3541,11 +3585,11 @@
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
       <c r="I54" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J54" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K54" s="22"/>
@@ -3563,11 +3607,11 @@
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
       <c r="I55" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J55" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K55" s="22"/>
@@ -3585,11 +3629,11 @@
       <c r="G56" s="20"/>
       <c r="H56" s="20"/>
       <c r="I56" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J56" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K56" s="22"/>
@@ -3607,11 +3651,11 @@
       <c r="G57" s="20"/>
       <c r="H57" s="20"/>
       <c r="I57" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J57" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K57" s="22"/>
@@ -3629,11 +3673,11 @@
       <c r="G58" s="20"/>
       <c r="H58" s="20"/>
       <c r="I58" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J58" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K58" s="22"/>
@@ -3651,11 +3695,11 @@
       <c r="G59" s="20"/>
       <c r="H59" s="20"/>
       <c r="I59" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J59" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K59" s="22"/>
@@ -3673,11 +3717,11 @@
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
       <c r="I60" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J60" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K60" s="22"/>
@@ -3695,11 +3739,11 @@
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
       <c r="I61" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J61" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K61" s="22"/>
@@ -3717,11 +3761,11 @@
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
       <c r="I62" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J62" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K62" s="22"/>
@@ -3739,11 +3783,11 @@
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
       <c r="I63" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J63" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K63" s="22"/>
@@ -3761,11 +3805,11 @@
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
       <c r="I64" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J64" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K64" s="22"/>
@@ -3783,11 +3827,11 @@
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
       <c r="I65" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J65" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K65" s="22"/>
@@ -3805,11 +3849,11 @@
       <c r="G66" s="20"/>
       <c r="H66" s="20"/>
       <c r="I66" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J66" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K66" s="22"/>
@@ -3827,11 +3871,11 @@
       <c r="G67" s="20"/>
       <c r="H67" s="20"/>
       <c r="I67" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J67" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K67" s="22"/>
@@ -3849,11 +3893,11 @@
       <c r="G68" s="20"/>
       <c r="H68" s="20"/>
       <c r="I68" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J68" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K68" s="22"/>
@@ -3871,11 +3915,11 @@
       <c r="G69" s="20"/>
       <c r="H69" s="20"/>
       <c r="I69" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J69" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K69" s="22"/>
@@ -3893,11 +3937,11 @@
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
       <c r="I70" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J70" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K70" s="22"/>
@@ -3915,11 +3959,11 @@
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
       <c r="I71" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J71" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K71" s="22"/>
@@ -3937,11 +3981,11 @@
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
       <c r="I72" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J72" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="22"/>
@@ -3959,11 +4003,11 @@
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
       <c r="I73" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="22"/>
@@ -3981,11 +4025,11 @@
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
       <c r="I74" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K74" s="22"/>
@@ -4003,11 +4047,11 @@
       <c r="G75" s="20"/>
       <c r="H75" s="20"/>
       <c r="I75" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K75" s="22"/>
@@ -4025,11 +4069,11 @@
       <c r="G76" s="20"/>
       <c r="H76" s="20"/>
       <c r="I76" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K76" s="22"/>
@@ -4047,11 +4091,11 @@
       <c r="G77" s="20"/>
       <c r="H77" s="20"/>
       <c r="I77" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K77" s="22"/>
@@ -4069,11 +4113,11 @@
       <c r="G78" s="20"/>
       <c r="H78" s="20"/>
       <c r="I78" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K78" s="22"/>
@@ -4091,11 +4135,11 @@
       <c r="G79" s="20"/>
       <c r="H79" s="20"/>
       <c r="I79" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K79" s="22"/>
@@ -4113,11 +4157,11 @@
       <c r="G80" s="20"/>
       <c r="H80" s="20"/>
       <c r="I80" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K80" s="22"/>
@@ -4135,11 +4179,11 @@
       <c r="G81" s="20"/>
       <c r="H81" s="20"/>
       <c r="I81" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K81" s="22"/>
@@ -4157,11 +4201,11 @@
       <c r="G82" s="20"/>
       <c r="H82" s="20"/>
       <c r="I82" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K82" s="22"/>
@@ -4179,11 +4223,11 @@
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
       <c r="I83" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K83" s="22"/>
@@ -4201,11 +4245,11 @@
       <c r="G84" s="20"/>
       <c r="H84" s="20"/>
       <c r="I84" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K84" s="22"/>
@@ -4223,11 +4267,11 @@
       <c r="G85" s="20"/>
       <c r="H85" s="20"/>
       <c r="I85" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K85" s="22"/>
@@ -4245,11 +4289,11 @@
       <c r="G86" s="20"/>
       <c r="H86" s="20"/>
       <c r="I86" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K86" s="22"/>
@@ -4267,11 +4311,11 @@
       <c r="G87" s="20"/>
       <c r="H87" s="20"/>
       <c r="I87" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="22"/>
@@ -4289,11 +4333,11 @@
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
       <c r="I88" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="22"/>
@@ -4311,11 +4355,11 @@
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
       <c r="I89" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="22"/>
@@ -4333,11 +4377,11 @@
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
       <c r="I90" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="22"/>
@@ -4355,11 +4399,11 @@
       <c r="G91" s="20"/>
       <c r="H91" s="20"/>
       <c r="I91" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="22"/>
@@ -4377,11 +4421,11 @@
       <c r="G92" s="20"/>
       <c r="H92" s="20"/>
       <c r="I92" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="22"/>
@@ -4399,11 +4443,11 @@
       <c r="G93" s="20"/>
       <c r="H93" s="20"/>
       <c r="I93" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="22"/>
@@ -4421,11 +4465,11 @@
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
       <c r="I94" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="22"/>
@@ -4443,11 +4487,11 @@
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
       <c r="I95" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="22"/>
@@ -4465,11 +4509,11 @@
       <c r="G96" s="20"/>
       <c r="H96" s="20"/>
       <c r="I96" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="22"/>
@@ -4487,11 +4531,11 @@
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
       <c r="I97" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="22"/>
@@ -4509,11 +4553,11 @@
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
       <c r="I98" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="22"/>
@@ -4531,11 +4575,11 @@
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
       <c r="I99" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="22"/>
@@ -4553,11 +4597,11 @@
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
       <c r="I100" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="22"/>
@@ -4575,11 +4619,11 @@
       <c r="G101" s="20"/>
       <c r="H101" s="20"/>
       <c r="I101" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J101" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="22"/>
@@ -4597,11 +4641,11 @@
       <c r="G102" s="20"/>
       <c r="H102" s="20"/>
       <c r="I102" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J102" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="22"/>
@@ -4619,11 +4663,11 @@
       <c r="G103" s="20"/>
       <c r="H103" s="20"/>
       <c r="I103" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J103" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="22"/>
@@ -4641,11 +4685,11 @@
       <c r="G104" s="20"/>
       <c r="H104" s="20"/>
       <c r="I104" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J104" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="22"/>
@@ -4663,11 +4707,11 @@
       <c r="G105" s="20"/>
       <c r="H105" s="20"/>
       <c r="I105" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J105" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="22"/>
@@ -4685,11 +4729,11 @@
       <c r="G106" s="20"/>
       <c r="H106" s="20"/>
       <c r="I106" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J106" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="22"/>
@@ -4707,11 +4751,11 @@
       <c r="G107" s="20"/>
       <c r="H107" s="20"/>
       <c r="I107" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J107" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="22"/>
@@ -4729,11 +4773,11 @@
       <c r="G108" s="20"/>
       <c r="H108" s="20"/>
       <c r="I108" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J108" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="22"/>
@@ -4751,11 +4795,11 @@
       <c r="G109" s="20"/>
       <c r="H109" s="20"/>
       <c r="I109" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J109" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="22"/>
@@ -4773,11 +4817,11 @@
       <c r="G110" s="20"/>
       <c r="H110" s="20"/>
       <c r="I110" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J110" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="22"/>
@@ -4795,11 +4839,11 @@
       <c r="G111" s="20"/>
       <c r="H111" s="20"/>
       <c r="I111" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J111" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="22"/>
@@ -4817,11 +4861,11 @@
       <c r="G112" s="20"/>
       <c r="H112" s="20"/>
       <c r="I112" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J112" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="22"/>
@@ -4839,11 +4883,11 @@
       <c r="G113" s="20"/>
       <c r="H113" s="20"/>
       <c r="I113" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J113" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="22"/>
@@ -4861,11 +4905,11 @@
       <c r="G114" s="20"/>
       <c r="H114" s="20"/>
       <c r="I114" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J114" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="22"/>
@@ -4883,11 +4927,11 @@
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
       <c r="I115" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J115" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="22"/>
@@ -4905,11 +4949,11 @@
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
       <c r="I116" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J116" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="22"/>
@@ -4927,11 +4971,11 @@
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
       <c r="I117" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J117" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="22"/>
@@ -4949,11 +4993,11 @@
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
       <c r="I118" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J118" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="22"/>
@@ -4971,11 +5015,11 @@
       <c r="G119" s="20"/>
       <c r="H119" s="20"/>
       <c r="I119" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J119" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="22"/>
@@ -4993,11 +5037,11 @@
       <c r="G120" s="20"/>
       <c r="H120" s="20"/>
       <c r="I120" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J120" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="22"/>
@@ -5015,11 +5059,11 @@
       <c r="G121" s="20"/>
       <c r="H121" s="20"/>
       <c r="I121" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J121" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="22"/>
@@ -5037,11 +5081,11 @@
       <c r="G122" s="20"/>
       <c r="H122" s="20"/>
       <c r="I122" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J122" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="22"/>
@@ -5059,11 +5103,11 @@
       <c r="G123" s="20"/>
       <c r="H123" s="20"/>
       <c r="I123" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J123" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="22"/>
@@ -5081,11 +5125,11 @@
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
       <c r="I124" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J124" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="22"/>
@@ -5103,11 +5147,11 @@
       <c r="G125" s="20"/>
       <c r="H125" s="20"/>
       <c r="I125" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J125" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="22"/>
@@ -5125,11 +5169,11 @@
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
       <c r="I126" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J126" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="22"/>
@@ -5147,11 +5191,11 @@
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
       <c r="I127" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J127" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="22"/>
@@ -5169,11 +5213,11 @@
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
       <c r="I128" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J128" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K128" s="22"/>
@@ -5191,11 +5235,11 @@
       <c r="G129" s="20"/>
       <c r="H129" s="20"/>
       <c r="I129" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J129" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K129" s="22"/>
@@ -5213,11 +5257,11 @@
       <c r="G130" s="20"/>
       <c r="H130" s="20"/>
       <c r="I130" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J130" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K130" s="22"/>
@@ -5235,11 +5279,11 @@
       <c r="G131" s="20"/>
       <c r="H131" s="20"/>
       <c r="I131" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J131" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K131" s="22"/>
@@ -5257,11 +5301,11 @@
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
       <c r="I132" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J132" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K132" s="22"/>
@@ -5279,11 +5323,11 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
       <c r="I133" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J133" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K133" s="22"/>
@@ -5301,11 +5345,11 @@
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
       <c r="I134" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J134" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K134" s="22"/>
@@ -5323,11 +5367,11 @@
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
       <c r="I135" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J135" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K135" s="22"/>
@@ -5345,11 +5389,11 @@
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
       <c r="I136" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J136" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K136" s="22"/>
@@ -5367,11 +5411,11 @@
       <c r="G137" s="20"/>
       <c r="H137" s="20"/>
       <c r="I137" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J137" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K137" s="22"/>
@@ -5389,11 +5433,11 @@
       <c r="G138" s="20"/>
       <c r="H138" s="20"/>
       <c r="I138" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J138" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K138" s="22"/>
@@ -5411,11 +5455,11 @@
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
       <c r="I139" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J139" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K139" s="22"/>
@@ -5433,11 +5477,11 @@
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
       <c r="I140" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J140" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K140" s="22"/>
@@ -5455,11 +5499,11 @@
       <c r="G141" s="20"/>
       <c r="H141" s="20"/>
       <c r="I141" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J141" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K141" s="22"/>
@@ -5477,11 +5521,11 @@
       <c r="G142" s="20"/>
       <c r="H142" s="20"/>
       <c r="I142" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J142" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K142" s="22"/>
@@ -5499,11 +5543,11 @@
       <c r="G143" s="20"/>
       <c r="H143" s="20"/>
       <c r="I143" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J143" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K143" s="22"/>
@@ -5521,11 +5565,11 @@
       <c r="G144" s="20"/>
       <c r="H144" s="20"/>
       <c r="I144" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J144" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K144" s="22"/>
@@ -5543,11 +5587,11 @@
       <c r="G145" s="20"/>
       <c r="H145" s="20"/>
       <c r="I145" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J145" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K145" s="22"/>
@@ -5565,11 +5609,11 @@
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
       <c r="I146" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J146" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K146" s="22"/>
@@ -5587,11 +5631,11 @@
       <c r="G147" s="20"/>
       <c r="H147" s="20"/>
       <c r="I147" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J147" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K147" s="22"/>
@@ -5609,11 +5653,11 @@
       <c r="G148" s="20"/>
       <c r="H148" s="20"/>
       <c r="I148" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J148" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K148" s="22"/>
@@ -5631,11 +5675,11 @@
       <c r="G149" s="20"/>
       <c r="H149" s="20"/>
       <c r="I149" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J149" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K149" s="22"/>
@@ -5653,11 +5697,11 @@
       <c r="G150" s="20"/>
       <c r="H150" s="20"/>
       <c r="I150" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J150" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K150" s="22"/>
@@ -5675,11 +5719,11 @@
       <c r="G151" s="20"/>
       <c r="H151" s="20"/>
       <c r="I151" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J151" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K151" s="22"/>
@@ -5697,11 +5741,11 @@
       <c r="G152" s="20"/>
       <c r="H152" s="20"/>
       <c r="I152" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J152" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K152" s="22"/>
@@ -5719,11 +5763,11 @@
       <c r="G153" s="20"/>
       <c r="H153" s="20"/>
       <c r="I153" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J153" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K153" s="22"/>
@@ -5741,11 +5785,11 @@
       <c r="G154" s="20"/>
       <c r="H154" s="20"/>
       <c r="I154" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J154" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K154" s="22"/>
@@ -5763,11 +5807,11 @@
       <c r="G155" s="20"/>
       <c r="H155" s="20"/>
       <c r="I155" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J155" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K155" s="22"/>
@@ -5785,11 +5829,11 @@
       <c r="G156" s="20"/>
       <c r="H156" s="20"/>
       <c r="I156" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J156" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K156" s="22"/>
@@ -5807,11 +5851,11 @@
       <c r="G157" s="20"/>
       <c r="H157" s="20"/>
       <c r="I157" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J157" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K157" s="22"/>
@@ -5829,11 +5873,11 @@
       <c r="G158" s="20"/>
       <c r="H158" s="20"/>
       <c r="I158" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J158" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K158" s="22"/>
@@ -5851,11 +5895,11 @@
       <c r="G159" s="20"/>
       <c r="H159" s="20"/>
       <c r="I159" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J159" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K159" s="22"/>
@@ -5873,11 +5917,11 @@
       <c r="G160" s="20"/>
       <c r="H160" s="20"/>
       <c r="I160" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J160" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K160" s="22"/>
@@ -5895,11 +5939,11 @@
       <c r="G161" s="20"/>
       <c r="H161" s="20"/>
       <c r="I161" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J161" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K161" s="22"/>
@@ -5917,11 +5961,11 @@
       <c r="G162" s="20"/>
       <c r="H162" s="20"/>
       <c r="I162" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J162" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K162" s="22"/>
@@ -5939,11 +5983,11 @@
       <c r="G163" s="20"/>
       <c r="H163" s="20"/>
       <c r="I163" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J163" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K163" s="22"/>
@@ -5961,11 +6005,11 @@
       <c r="G164" s="20"/>
       <c r="H164" s="20"/>
       <c r="I164" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J164" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K164" s="22"/>
@@ -5983,11 +6027,11 @@
       <c r="G165" s="20"/>
       <c r="H165" s="20"/>
       <c r="I165" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J165" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K165" s="22"/>
@@ -6005,11 +6049,11 @@
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
       <c r="I166" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J166" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K166" s="22"/>
@@ -6027,11 +6071,11 @@
       <c r="G167" s="20"/>
       <c r="H167" s="20"/>
       <c r="I167" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J167" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K167" s="22"/>
@@ -6049,11 +6093,11 @@
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
       <c r="I168" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J168" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K168" s="22"/>
@@ -6071,11 +6115,11 @@
       <c r="G169" s="20"/>
       <c r="H169" s="20"/>
       <c r="I169" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J169" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K169" s="22"/>
@@ -6093,11 +6137,11 @@
       <c r="G170" s="20"/>
       <c r="H170" s="20"/>
       <c r="I170" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J170" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K170" s="22"/>
@@ -6115,11 +6159,11 @@
       <c r="G171" s="20"/>
       <c r="H171" s="20"/>
       <c r="I171" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J171" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K171" s="22"/>
@@ -6137,11 +6181,11 @@
       <c r="G172" s="20"/>
       <c r="H172" s="20"/>
       <c r="I172" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J172" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K172" s="22"/>
@@ -6159,11 +6203,11 @@
       <c r="G173" s="20"/>
       <c r="H173" s="20"/>
       <c r="I173" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J173" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K173" s="22"/>
@@ -6181,11 +6225,11 @@
       <c r="G174" s="20"/>
       <c r="H174" s="20"/>
       <c r="I174" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J174" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K174" s="22"/>
@@ -6203,11 +6247,11 @@
       <c r="G175" s="20"/>
       <c r="H175" s="20"/>
       <c r="I175" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J175" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K175" s="22"/>
@@ -6225,11 +6269,11 @@
       <c r="G176" s="20"/>
       <c r="H176" s="20"/>
       <c r="I176" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J176" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K176" s="22"/>
@@ -6247,11 +6291,11 @@
       <c r="G177" s="20"/>
       <c r="H177" s="20"/>
       <c r="I177" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J177" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K177" s="22"/>
@@ -6269,11 +6313,11 @@
       <c r="G178" s="20"/>
       <c r="H178" s="20"/>
       <c r="I178" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J178" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K178" s="22"/>
@@ -6291,11 +6335,11 @@
       <c r="G179" s="20"/>
       <c r="H179" s="20"/>
       <c r="I179" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J179" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K179" s="22"/>
@@ -6313,11 +6357,11 @@
       <c r="G180" s="20"/>
       <c r="H180" s="20"/>
       <c r="I180" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J180" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K180" s="22"/>
@@ -6335,11 +6379,11 @@
       <c r="G181" s="20"/>
       <c r="H181" s="20"/>
       <c r="I181" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J181" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K181" s="22"/>
@@ -6357,11 +6401,11 @@
       <c r="G182" s="20"/>
       <c r="H182" s="20"/>
       <c r="I182" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J182" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K182" s="22"/>
@@ -6379,11 +6423,11 @@
       <c r="G183" s="20"/>
       <c r="H183" s="20"/>
       <c r="I183" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J183" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K183" s="22"/>
@@ -6401,11 +6445,11 @@
       <c r="G184" s="20"/>
       <c r="H184" s="20"/>
       <c r="I184" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J184" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K184" s="22"/>
@@ -6423,11 +6467,11 @@
       <c r="G185" s="20"/>
       <c r="H185" s="20"/>
       <c r="I185" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J185" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K185" s="22"/>
@@ -6445,11 +6489,11 @@
       <c r="G186" s="20"/>
       <c r="H186" s="20"/>
       <c r="I186" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J186" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K186" s="22"/>
@@ -6467,11 +6511,11 @@
       <c r="G187" s="20"/>
       <c r="H187" s="20"/>
       <c r="I187" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J187" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K187" s="22"/>
@@ -6489,11 +6533,11 @@
       <c r="G188" s="20"/>
       <c r="H188" s="20"/>
       <c r="I188" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J188" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K188" s="22"/>
@@ -6511,11 +6555,11 @@
       <c r="G189" s="20"/>
       <c r="H189" s="20"/>
       <c r="I189" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J189" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K189" s="22"/>
@@ -6533,11 +6577,11 @@
       <c r="G190" s="20"/>
       <c r="H190" s="20"/>
       <c r="I190" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J190" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K190" s="22"/>
@@ -6555,11 +6599,11 @@
       <c r="G191" s="20"/>
       <c r="H191" s="20"/>
       <c r="I191" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J191" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K191" s="22"/>
@@ -6577,11 +6621,11 @@
       <c r="G192" s="20"/>
       <c r="H192" s="20"/>
       <c r="I192" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J192" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K192" s="22"/>
@@ -6599,11 +6643,11 @@
       <c r="G193" s="20"/>
       <c r="H193" s="20"/>
       <c r="I193" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J193" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K193" s="22"/>
@@ -6621,11 +6665,11 @@
       <c r="G194" s="20"/>
       <c r="H194" s="20"/>
       <c r="I194" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J194" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K194" s="22"/>
@@ -6643,11 +6687,11 @@
       <c r="G195" s="20"/>
       <c r="H195" s="20"/>
       <c r="I195" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J195" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K195" s="22"/>
@@ -6665,11 +6709,11 @@
       <c r="G196" s="20"/>
       <c r="H196" s="20"/>
       <c r="I196" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J196" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K196" s="22"/>
@@ -6687,11 +6731,11 @@
       <c r="G197" s="20"/>
       <c r="H197" s="20"/>
       <c r="I197" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J197" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K197" s="22"/>
@@ -6709,11 +6753,11 @@
       <c r="G198" s="20"/>
       <c r="H198" s="20"/>
       <c r="I198" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J198" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K198" s="22"/>
@@ -6731,11 +6775,11 @@
       <c r="G199" s="20"/>
       <c r="H199" s="20"/>
       <c r="I199" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J199" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K199" s="22"/>
@@ -6753,11 +6797,11 @@
       <c r="G200" s="20"/>
       <c r="H200" s="20"/>
       <c r="I200" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J200" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K200" s="22"/>
@@ -6775,11 +6819,11 @@
       <c r="G201" s="20"/>
       <c r="H201" s="20"/>
       <c r="I201" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J201" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K201" s="22"/>
@@ -6797,11 +6841,11 @@
       <c r="G202" s="20"/>
       <c r="H202" s="20"/>
       <c r="I202" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J202" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K202" s="22"/>
@@ -6819,11 +6863,11 @@
       <c r="G203" s="20"/>
       <c r="H203" s="20"/>
       <c r="I203" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J203" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K203" s="22"/>
@@ -6841,11 +6885,11 @@
       <c r="G204" s="20"/>
       <c r="H204" s="20"/>
       <c r="I204" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J204" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K204" s="22"/>
@@ -6863,11 +6907,11 @@
       <c r="G205" s="20"/>
       <c r="H205" s="20"/>
       <c r="I205" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J205" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K205" s="22"/>
@@ -6885,11 +6929,11 @@
       <c r="G206" s="20"/>
       <c r="H206" s="20"/>
       <c r="I206" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J206" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K206" s="22"/>
@@ -6907,11 +6951,11 @@
       <c r="G207" s="20"/>
       <c r="H207" s="20"/>
       <c r="I207" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J207" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K207" s="22"/>
@@ -6929,11 +6973,11 @@
       <c r="G208" s="20"/>
       <c r="H208" s="20"/>
       <c r="I208" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J208" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K208" s="22"/>
@@ -6951,11 +6995,11 @@
       <c r="G209" s="20"/>
       <c r="H209" s="20"/>
       <c r="I209" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J209" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K209" s="22"/>
@@ -6973,11 +7017,11 @@
       <c r="G210" s="20"/>
       <c r="H210" s="20"/>
       <c r="I210" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J210" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K210" s="22"/>
@@ -6995,11 +7039,11 @@
       <c r="G211" s="20"/>
       <c r="H211" s="20"/>
       <c r="I211" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J211" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K211" s="22"/>
@@ -7017,11 +7061,11 @@
       <c r="G212" s="20"/>
       <c r="H212" s="20"/>
       <c r="I212" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J212" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K212" s="22"/>
@@ -7039,11 +7083,11 @@
       <c r="G213" s="20"/>
       <c r="H213" s="20"/>
       <c r="I213" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J213" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K213" s="22"/>
@@ -7061,11 +7105,11 @@
       <c r="G214" s="20"/>
       <c r="H214" s="20"/>
       <c r="I214" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J214" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K214" s="22"/>
@@ -7083,11 +7127,11 @@
       <c r="G215" s="20"/>
       <c r="H215" s="20"/>
       <c r="I215" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J215" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K215" s="22"/>
@@ -7105,11 +7149,11 @@
       <c r="G216" s="20"/>
       <c r="H216" s="20"/>
       <c r="I216" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J216" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K216" s="22"/>
@@ -7127,11 +7171,11 @@
       <c r="G217" s="20"/>
       <c r="H217" s="20"/>
       <c r="I217" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J217" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K217" s="22"/>
@@ -7149,11 +7193,11 @@
       <c r="G218" s="20"/>
       <c r="H218" s="20"/>
       <c r="I218" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J218" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K218" s="22"/>
@@ -7171,11 +7215,11 @@
       <c r="G219" s="20"/>
       <c r="H219" s="20"/>
       <c r="I219" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J219" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K219" s="22"/>
@@ -7193,11 +7237,11 @@
       <c r="G220" s="20"/>
       <c r="H220" s="20"/>
       <c r="I220" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J220" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K220" s="22"/>
@@ -7215,11 +7259,11 @@
       <c r="G221" s="20"/>
       <c r="H221" s="20"/>
       <c r="I221" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J221" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K221" s="22"/>
@@ -7237,11 +7281,11 @@
       <c r="G222" s="20"/>
       <c r="H222" s="20"/>
       <c r="I222" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J222" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K222" s="22"/>
@@ -7259,11 +7303,11 @@
       <c r="G223" s="20"/>
       <c r="H223" s="20"/>
       <c r="I223" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J223" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K223" s="22"/>
@@ -7281,11 +7325,11 @@
       <c r="G224" s="20"/>
       <c r="H224" s="20"/>
       <c r="I224" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J224" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K224" s="22"/>
@@ -7303,11 +7347,11 @@
       <c r="G225" s="20"/>
       <c r="H225" s="20"/>
       <c r="I225" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J225" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K225" s="22"/>
@@ -7325,11 +7369,11 @@
       <c r="G226" s="20"/>
       <c r="H226" s="20"/>
       <c r="I226" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J226" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K226" s="22"/>
@@ -7347,11 +7391,11 @@
       <c r="G227" s="20"/>
       <c r="H227" s="20"/>
       <c r="I227" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J227" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K227" s="22"/>
@@ -7369,11 +7413,11 @@
       <c r="G228" s="20"/>
       <c r="H228" s="20"/>
       <c r="I228" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J228" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K228" s="22"/>
@@ -7391,11 +7435,11 @@
       <c r="G229" s="20"/>
       <c r="H229" s="20"/>
       <c r="I229" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J229" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K229" s="22"/>
@@ -7413,11 +7457,11 @@
       <c r="G230" s="20"/>
       <c r="H230" s="20"/>
       <c r="I230" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J230" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K230" s="22"/>
@@ -7435,11 +7479,11 @@
       <c r="G231" s="20"/>
       <c r="H231" s="20"/>
       <c r="I231" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J231" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K231" s="22"/>
@@ -7457,11 +7501,11 @@
       <c r="G232" s="20"/>
       <c r="H232" s="20"/>
       <c r="I232" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J232" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K232" s="22"/>
@@ -7479,11 +7523,11 @@
       <c r="G233" s="20"/>
       <c r="H233" s="20"/>
       <c r="I233" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J233" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K233" s="22"/>
@@ -7501,11 +7545,11 @@
       <c r="G234" s="20"/>
       <c r="H234" s="20"/>
       <c r="I234" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J234" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K234" s="22"/>
@@ -7523,11 +7567,11 @@
       <c r="G235" s="20"/>
       <c r="H235" s="20"/>
       <c r="I235" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J235" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K235" s="22"/>
@@ -7545,11 +7589,11 @@
       <c r="G236" s="20"/>
       <c r="H236" s="20"/>
       <c r="I236" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J236" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K236" s="22"/>
@@ -7567,11 +7611,11 @@
       <c r="G237" s="20"/>
       <c r="H237" s="20"/>
       <c r="I237" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J237" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K237" s="22"/>
@@ -7589,11 +7633,11 @@
       <c r="G238" s="20"/>
       <c r="H238" s="20"/>
       <c r="I238" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J238" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K238" s="22"/>
@@ -7611,11 +7655,11 @@
       <c r="G239" s="20"/>
       <c r="H239" s="20"/>
       <c r="I239" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J239" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K239" s="22"/>
@@ -7633,11 +7677,11 @@
       <c r="G240" s="20"/>
       <c r="H240" s="20"/>
       <c r="I240" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J240" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K240" s="22"/>
@@ -7655,11 +7699,11 @@
       <c r="G241" s="20"/>
       <c r="H241" s="20"/>
       <c r="I241" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J241" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K241" s="22"/>
@@ -7677,11 +7721,11 @@
       <c r="G242" s="20"/>
       <c r="H242" s="20"/>
       <c r="I242" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J242" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K242" s="22"/>
@@ -7699,11 +7743,11 @@
       <c r="G243" s="20"/>
       <c r="H243" s="20"/>
       <c r="I243" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J243" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K243" s="22"/>
@@ -7721,11 +7765,11 @@
       <c r="G244" s="20"/>
       <c r="H244" s="20"/>
       <c r="I244" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J244" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K244" s="22"/>
@@ -7743,11 +7787,11 @@
       <c r="G245" s="20"/>
       <c r="H245" s="20"/>
       <c r="I245" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J245" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K245" s="22"/>
@@ -7765,11 +7809,11 @@
       <c r="G246" s="20"/>
       <c r="H246" s="20"/>
       <c r="I246" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J246" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K246" s="22"/>
@@ -7787,11 +7831,11 @@
       <c r="G247" s="20"/>
       <c r="H247" s="20"/>
       <c r="I247" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J247" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K247" s="22"/>
@@ -7809,11 +7853,11 @@
       <c r="G248" s="20"/>
       <c r="H248" s="20"/>
       <c r="I248" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J248" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K248" s="22"/>
@@ -7831,11 +7875,11 @@
       <c r="G249" s="20"/>
       <c r="H249" s="20"/>
       <c r="I249" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J249" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K249" s="22"/>
@@ -7853,11 +7897,11 @@
       <c r="G250" s="20"/>
       <c r="H250" s="20"/>
       <c r="I250" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J250" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K250" s="22"/>
@@ -7875,11 +7919,11 @@
       <c r="G251" s="20"/>
       <c r="H251" s="20"/>
       <c r="I251" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J251" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K251" s="22"/>
@@ -7897,11 +7941,11 @@
       <c r="G252" s="20"/>
       <c r="H252" s="20"/>
       <c r="I252" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J252" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K252" s="22"/>
@@ -7919,11 +7963,11 @@
       <c r="G253" s="20"/>
       <c r="H253" s="20"/>
       <c r="I253" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J253" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K253" s="22"/>
@@ -7941,11 +7985,11 @@
       <c r="G254" s="20"/>
       <c r="H254" s="20"/>
       <c r="I254" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J254" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K254" s="22"/>
@@ -7963,11 +8007,11 @@
       <c r="G255" s="20"/>
       <c r="H255" s="20"/>
       <c r="I255" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J255" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K255" s="22"/>
@@ -7985,11 +8029,11 @@
       <c r="G256" s="20"/>
       <c r="H256" s="20"/>
       <c r="I256" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J256" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K256" s="22"/>
@@ -8007,11 +8051,11 @@
       <c r="G257" s="20"/>
       <c r="H257" s="20"/>
       <c r="I257" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J257" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K257" s="22"/>
@@ -8029,11 +8073,11 @@
       <c r="G258" s="20"/>
       <c r="H258" s="20"/>
       <c r="I258" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K258" s="22"/>
@@ -8051,11 +8095,11 @@
       <c r="G259" s="20"/>
       <c r="H259" s="20"/>
       <c r="I259" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J259" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K259" s="22"/>
@@ -8073,11 +8117,11 @@
       <c r="G260" s="20"/>
       <c r="H260" s="20"/>
       <c r="I260" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J260" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K260" s="22"/>
@@ -8095,11 +8139,11 @@
       <c r="G261" s="20"/>
       <c r="H261" s="20"/>
       <c r="I261" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J261" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K261" s="22"/>
@@ -8117,11 +8161,11 @@
       <c r="G262" s="20"/>
       <c r="H262" s="20"/>
       <c r="I262" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J262" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K262" s="22"/>
@@ -8139,11 +8183,11 @@
       <c r="G263" s="20"/>
       <c r="H263" s="20"/>
       <c r="I263" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J263" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K263" s="22"/>
@@ -8161,11 +8205,11 @@
       <c r="G264" s="20"/>
       <c r="H264" s="20"/>
       <c r="I264" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J264" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K264" s="22"/>
@@ -8183,11 +8227,11 @@
       <c r="G265" s="20"/>
       <c r="H265" s="20"/>
       <c r="I265" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J265" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K265" s="22"/>
@@ -8205,11 +8249,11 @@
       <c r="G266" s="20"/>
       <c r="H266" s="20"/>
       <c r="I266" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J266" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K266" s="22"/>
@@ -8227,11 +8271,11 @@
       <c r="G267" s="20"/>
       <c r="H267" s="20"/>
       <c r="I267" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J267" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K267" s="22"/>
@@ -8249,11 +8293,11 @@
       <c r="G268" s="20"/>
       <c r="H268" s="20"/>
       <c r="I268" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J268" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K268" s="22"/>
@@ -8271,11 +8315,11 @@
       <c r="G269" s="20"/>
       <c r="H269" s="20"/>
       <c r="I269" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J269" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K269" s="22"/>
@@ -8293,11 +8337,11 @@
       <c r="G270" s="20"/>
       <c r="H270" s="20"/>
       <c r="I270" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J270" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K270" s="22"/>
@@ -8315,11 +8359,11 @@
       <c r="G271" s="20"/>
       <c r="H271" s="20"/>
       <c r="I271" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J271" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K271" s="22"/>
@@ -8337,11 +8381,11 @@
       <c r="G272" s="20"/>
       <c r="H272" s="20"/>
       <c r="I272" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J272" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K272" s="22"/>
@@ -8359,11 +8403,11 @@
       <c r="G273" s="20"/>
       <c r="H273" s="20"/>
       <c r="I273" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J273" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K273" s="22"/>
@@ -8381,11 +8425,11 @@
       <c r="G274" s="20"/>
       <c r="H274" s="20"/>
       <c r="I274" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J274" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K274" s="22"/>
@@ -8403,11 +8447,11 @@
       <c r="G275" s="20"/>
       <c r="H275" s="20"/>
       <c r="I275" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J275" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K275" s="22"/>
@@ -8425,11 +8469,11 @@
       <c r="G276" s="20"/>
       <c r="H276" s="20"/>
       <c r="I276" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J276" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K276" s="22"/>
@@ -8447,11 +8491,11 @@
       <c r="G277" s="20"/>
       <c r="H277" s="20"/>
       <c r="I277" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J277" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K277" s="22"/>
@@ -8469,11 +8513,11 @@
       <c r="G278" s="20"/>
       <c r="H278" s="20"/>
       <c r="I278" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J278" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K278" s="22"/>
@@ -8491,11 +8535,11 @@
       <c r="G279" s="20"/>
       <c r="H279" s="20"/>
       <c r="I279" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J279" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K279" s="22"/>
@@ -8513,11 +8557,11 @@
       <c r="G280" s="20"/>
       <c r="H280" s="20"/>
       <c r="I280" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J280" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K280" s="22"/>
@@ -8535,11 +8579,11 @@
       <c r="G281" s="20"/>
       <c r="H281" s="20"/>
       <c r="I281" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J281" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K281" s="22"/>
@@ -8557,11 +8601,11 @@
       <c r="G282" s="20"/>
       <c r="H282" s="20"/>
       <c r="I282" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J282" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K282" s="22"/>
@@ -8579,11 +8623,11 @@
       <c r="G283" s="20"/>
       <c r="H283" s="20"/>
       <c r="I283" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J283" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K283" s="22"/>
@@ -8601,11 +8645,11 @@
       <c r="G284" s="20"/>
       <c r="H284" s="20"/>
       <c r="I284" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J284" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K284" s="22"/>
@@ -8623,11 +8667,11 @@
       <c r="G285" s="20"/>
       <c r="H285" s="20"/>
       <c r="I285" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J285" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K285" s="22"/>
@@ -8645,11 +8689,11 @@
       <c r="G286" s="20"/>
       <c r="H286" s="20"/>
       <c r="I286" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J286" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K286" s="22"/>
@@ -8667,11 +8711,11 @@
       <c r="G287" s="20"/>
       <c r="H287" s="20"/>
       <c r="I287" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J287" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K287" s="22"/>
@@ -8689,11 +8733,11 @@
       <c r="G288" s="20"/>
       <c r="H288" s="20"/>
       <c r="I288" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J288" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K288" s="22"/>
@@ -8711,11 +8755,11 @@
       <c r="G289" s="20"/>
       <c r="H289" s="20"/>
       <c r="I289" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J289" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K289" s="22"/>
@@ -8733,11 +8777,11 @@
       <c r="G290" s="20"/>
       <c r="H290" s="20"/>
       <c r="I290" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J290" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K290" s="22"/>
@@ -8755,11 +8799,11 @@
       <c r="G291" s="20"/>
       <c r="H291" s="20"/>
       <c r="I291" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J291" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K291" s="22"/>
@@ -8777,11 +8821,11 @@
       <c r="G292" s="20"/>
       <c r="H292" s="20"/>
       <c r="I292" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J292" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K292" s="22"/>
@@ -8799,11 +8843,11 @@
       <c r="G293" s="20"/>
       <c r="H293" s="20"/>
       <c r="I293" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J293" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K293" s="22"/>
@@ -8821,11 +8865,11 @@
       <c r="G294" s="20"/>
       <c r="H294" s="20"/>
       <c r="I294" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J294" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K294" s="22"/>
@@ -8843,11 +8887,11 @@
       <c r="G295" s="20"/>
       <c r="H295" s="20"/>
       <c r="I295" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J295" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K295" s="22"/>
@@ -8865,11 +8909,11 @@
       <c r="G296" s="20"/>
       <c r="H296" s="20"/>
       <c r="I296" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J296" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K296" s="22"/>
@@ -8887,11 +8931,11 @@
       <c r="G297" s="20"/>
       <c r="H297" s="20"/>
       <c r="I297" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J297" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K297" s="22"/>
@@ -8909,11 +8953,11 @@
       <c r="G298" s="20"/>
       <c r="H298" s="20"/>
       <c r="I298" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J298" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K298" s="22"/>
@@ -8931,11 +8975,11 @@
       <c r="G299" s="20"/>
       <c r="H299" s="20"/>
       <c r="I299" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J299" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K299" s="22"/>
@@ -8953,11 +8997,11 @@
       <c r="G300" s="20"/>
       <c r="H300" s="20"/>
       <c r="I300" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J300" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K300" s="22"/>
@@ -8975,11 +9019,11 @@
       <c r="G301" s="20"/>
       <c r="H301" s="20"/>
       <c r="I301" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J301" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K301" s="22"/>
@@ -8997,11 +9041,11 @@
       <c r="G302" s="20"/>
       <c r="H302" s="20"/>
       <c r="I302" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J302" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K302" s="22"/>
@@ -9019,11 +9063,11 @@
       <c r="G303" s="20"/>
       <c r="H303" s="20"/>
       <c r="I303" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J303" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K303" s="22"/>
@@ -9041,11 +9085,11 @@
       <c r="G304" s="20"/>
       <c r="H304" s="20"/>
       <c r="I304" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J304" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K304" s="22"/>
@@ -9063,11 +9107,11 @@
       <c r="G305" s="20"/>
       <c r="H305" s="20"/>
       <c r="I305" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J305" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K305" s="22"/>
@@ -9085,11 +9129,11 @@
       <c r="G306" s="20"/>
       <c r="H306" s="20"/>
       <c r="I306" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J306" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K306" s="22"/>
@@ -9107,11 +9151,11 @@
       <c r="G307" s="20"/>
       <c r="H307" s="20"/>
       <c r="I307" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J307" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K307" s="22"/>
@@ -9129,11 +9173,11 @@
       <c r="G308" s="20"/>
       <c r="H308" s="20"/>
       <c r="I308" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J308" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K308" s="22"/>
@@ -9151,11 +9195,11 @@
       <c r="G309" s="20"/>
       <c r="H309" s="20"/>
       <c r="I309" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J309" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K309" s="22"/>
@@ -9173,11 +9217,11 @@
       <c r="G310" s="20"/>
       <c r="H310" s="20"/>
       <c r="I310" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J310" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K310" s="22"/>
@@ -9195,11 +9239,11 @@
       <c r="G311" s="20"/>
       <c r="H311" s="20"/>
       <c r="I311" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J311" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K311" s="22"/>
@@ -9217,11 +9261,11 @@
       <c r="G312" s="20"/>
       <c r="H312" s="20"/>
       <c r="I312" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J312" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K312" s="22"/>
@@ -9239,11 +9283,11 @@
       <c r="G313" s="20"/>
       <c r="H313" s="20"/>
       <c r="I313" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J313" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K313" s="22"/>
@@ -9261,11 +9305,11 @@
       <c r="G314" s="20"/>
       <c r="H314" s="20"/>
       <c r="I314" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J314" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K314" s="22"/>
@@ -9283,11 +9327,11 @@
       <c r="G315" s="20"/>
       <c r="H315" s="20"/>
       <c r="I315" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J315" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K315" s="22"/>
@@ -9305,11 +9349,11 @@
       <c r="G316" s="20"/>
       <c r="H316" s="20"/>
       <c r="I316" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J316" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K316" s="22"/>
@@ -9327,11 +9371,11 @@
       <c r="G317" s="20"/>
       <c r="H317" s="20"/>
       <c r="I317" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J317" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K317" s="22"/>
@@ -9349,11 +9393,11 @@
       <c r="G318" s="20"/>
       <c r="H318" s="20"/>
       <c r="I318" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J318" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K318" s="22"/>
@@ -9371,11 +9415,11 @@
       <c r="G319" s="20"/>
       <c r="H319" s="20"/>
       <c r="I319" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J319" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K319" s="22"/>
@@ -9393,11 +9437,11 @@
       <c r="G320" s="20"/>
       <c r="H320" s="20"/>
       <c r="I320" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J320" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K320" s="22"/>
@@ -9415,11 +9459,11 @@
       <c r="G321" s="20"/>
       <c r="H321" s="20"/>
       <c r="I321" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J321" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K321" s="22"/>
@@ -9437,11 +9481,11 @@
       <c r="G322" s="20"/>
       <c r="H322" s="20"/>
       <c r="I322" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J322" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K322" s="22"/>
@@ -9459,11 +9503,11 @@
       <c r="G323" s="20"/>
       <c r="H323" s="20"/>
       <c r="I323" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J323" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K323" s="22"/>
@@ -9481,11 +9525,11 @@
       <c r="G324" s="20"/>
       <c r="H324" s="20"/>
       <c r="I324" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J324" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K324" s="22"/>
@@ -9503,11 +9547,11 @@
       <c r="G325" s="20"/>
       <c r="H325" s="20"/>
       <c r="I325" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J325" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K325" s="22"/>
@@ -9525,11 +9569,11 @@
       <c r="G326" s="20"/>
       <c r="H326" s="20"/>
       <c r="I326" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J326" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K326" s="22"/>
@@ -9547,11 +9591,11 @@
       <c r="G327" s="20"/>
       <c r="H327" s="20"/>
       <c r="I327" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J327" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K327" s="22"/>
@@ -9569,11 +9613,11 @@
       <c r="G328" s="20"/>
       <c r="H328" s="20"/>
       <c r="I328" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J328" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K328" s="22"/>
@@ -9591,11 +9635,11 @@
       <c r="G329" s="20"/>
       <c r="H329" s="20"/>
       <c r="I329" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J329" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K329" s="22"/>
@@ -9613,11 +9657,11 @@
       <c r="G330" s="20"/>
       <c r="H330" s="20"/>
       <c r="I330" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J330" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K330" s="22"/>
@@ -9635,11 +9679,11 @@
       <c r="G331" s="20"/>
       <c r="H331" s="20"/>
       <c r="I331" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J331" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K331" s="22"/>
@@ -9657,11 +9701,11 @@
       <c r="G332" s="20"/>
       <c r="H332" s="20"/>
       <c r="I332" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J332" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K332" s="22"/>
@@ -9679,11 +9723,11 @@
       <c r="G333" s="20"/>
       <c r="H333" s="20"/>
       <c r="I333" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J333" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K333" s="22"/>
@@ -9701,11 +9745,11 @@
       <c r="G334" s="20"/>
       <c r="H334" s="20"/>
       <c r="I334" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J334" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K334" s="22"/>
@@ -9723,11 +9767,11 @@
       <c r="G335" s="20"/>
       <c r="H335" s="20"/>
       <c r="I335" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J335" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K335" s="22"/>
@@ -9745,11 +9789,11 @@
       <c r="G336" s="20"/>
       <c r="H336" s="20"/>
       <c r="I336" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J336" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K336" s="22"/>
@@ -9767,11 +9811,11 @@
       <c r="G337" s="20"/>
       <c r="H337" s="20"/>
       <c r="I337" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J337" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K337" s="22"/>
@@ -9789,11 +9833,11 @@
       <c r="G338" s="20"/>
       <c r="H338" s="20"/>
       <c r="I338" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J338" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K338" s="22"/>
@@ -9811,11 +9855,11 @@
       <c r="G339" s="20"/>
       <c r="H339" s="20"/>
       <c r="I339" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J339" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K339" s="22"/>
@@ -9833,11 +9877,11 @@
       <c r="G340" s="20"/>
       <c r="H340" s="20"/>
       <c r="I340" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J340" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K340" s="22"/>
@@ -9855,11 +9899,11 @@
       <c r="G341" s="20"/>
       <c r="H341" s="20"/>
       <c r="I341" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J341" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K341" s="22"/>
@@ -9877,11 +9921,11 @@
       <c r="G342" s="20"/>
       <c r="H342" s="20"/>
       <c r="I342" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J342" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K342" s="22"/>
@@ -9899,11 +9943,11 @@
       <c r="G343" s="20"/>
       <c r="H343" s="20"/>
       <c r="I343" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J343" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K343" s="22"/>
@@ -9921,11 +9965,11 @@
       <c r="G344" s="20"/>
       <c r="H344" s="20"/>
       <c r="I344" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J344" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K344" s="22"/>
@@ -9943,11 +9987,11 @@
       <c r="G345" s="20"/>
       <c r="H345" s="20"/>
       <c r="I345" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J345" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K345" s="22"/>
@@ -9965,11 +10009,11 @@
       <c r="G346" s="20"/>
       <c r="H346" s="20"/>
       <c r="I346" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J346" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K346" s="22"/>
@@ -9987,11 +10031,11 @@
       <c r="G347" s="20"/>
       <c r="H347" s="20"/>
       <c r="I347" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J347" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K347" s="22"/>
@@ -10009,11 +10053,11 @@
       <c r="G348" s="20"/>
       <c r="H348" s="20"/>
       <c r="I348" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J348" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K348" s="22"/>
@@ -10031,11 +10075,11 @@
       <c r="G349" s="20"/>
       <c r="H349" s="20"/>
       <c r="I349" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J349" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K349" s="22"/>
@@ -10053,11 +10097,11 @@
       <c r="G350" s="20"/>
       <c r="H350" s="20"/>
       <c r="I350" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J350" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K350" s="22"/>
@@ -10075,11 +10119,11 @@
       <c r="G351" s="20"/>
       <c r="H351" s="20"/>
       <c r="I351" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J351" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K351" s="22"/>
@@ -10097,11 +10141,11 @@
       <c r="G352" s="20"/>
       <c r="H352" s="20"/>
       <c r="I352" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J352" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K352" s="22"/>
@@ -10119,11 +10163,11 @@
       <c r="G353" s="20"/>
       <c r="H353" s="20"/>
       <c r="I353" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J353" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K353" s="22"/>
@@ -10141,11 +10185,11 @@
       <c r="G354" s="20"/>
       <c r="H354" s="20"/>
       <c r="I354" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J354" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K354" s="22"/>
@@ -10163,11 +10207,11 @@
       <c r="G355" s="20"/>
       <c r="H355" s="20"/>
       <c r="I355" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J355" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K355" s="22"/>
@@ -10185,11 +10229,11 @@
       <c r="G356" s="20"/>
       <c r="H356" s="20"/>
       <c r="I356" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J356" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K356" s="22"/>
@@ -10207,11 +10251,11 @@
       <c r="G357" s="20"/>
       <c r="H357" s="20"/>
       <c r="I357" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J357" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K357" s="22"/>
@@ -10229,11 +10273,11 @@
       <c r="G358" s="20"/>
       <c r="H358" s="20"/>
       <c r="I358" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J358" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K358" s="22"/>
@@ -10251,11 +10295,11 @@
       <c r="G359" s="20"/>
       <c r="H359" s="20"/>
       <c r="I359" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J359" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K359" s="22"/>
@@ -10273,11 +10317,11 @@
       <c r="G360" s="20"/>
       <c r="H360" s="20"/>
       <c r="I360" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J360" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K360" s="22"/>
@@ -10295,11 +10339,11 @@
       <c r="G361" s="20"/>
       <c r="H361" s="20"/>
       <c r="I361" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J361" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K361" s="22"/>
@@ -10317,11 +10361,11 @@
       <c r="G362" s="20"/>
       <c r="H362" s="20"/>
       <c r="I362" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J362" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K362" s="22"/>
@@ -10339,11 +10383,11 @@
       <c r="G363" s="20"/>
       <c r="H363" s="20"/>
       <c r="I363" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J363" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K363" s="22"/>
@@ -10361,11 +10405,11 @@
       <c r="G364" s="20"/>
       <c r="H364" s="20"/>
       <c r="I364" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J364" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K364" s="22"/>
@@ -10383,11 +10427,11 @@
       <c r="G365" s="20"/>
       <c r="H365" s="20"/>
       <c r="I365" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J365" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K365" s="22"/>
@@ -10405,11 +10449,11 @@
       <c r="G366" s="20"/>
       <c r="H366" s="20"/>
       <c r="I366" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J366" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K366" s="22"/>
@@ -10427,11 +10471,11 @@
       <c r="G367" s="20"/>
       <c r="H367" s="20"/>
       <c r="I367" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J367" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K367" s="22"/>
@@ -10449,11 +10493,11 @@
       <c r="G368" s="20"/>
       <c r="H368" s="20"/>
       <c r="I368" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J368" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K368" s="22"/>
@@ -10471,11 +10515,11 @@
       <c r="G369" s="20"/>
       <c r="H369" s="20"/>
       <c r="I369" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J369" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K369" s="22"/>
@@ -10493,11 +10537,11 @@
       <c r="G370" s="20"/>
       <c r="H370" s="20"/>
       <c r="I370" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J370" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K370" s="22"/>
@@ -10515,11 +10559,11 @@
       <c r="G371" s="20"/>
       <c r="H371" s="20"/>
       <c r="I371" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J371" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K371" s="22"/>
@@ -10537,11 +10581,11 @@
       <c r="G372" s="20"/>
       <c r="H372" s="20"/>
       <c r="I372" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J372" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K372" s="22"/>
@@ -10559,11 +10603,11 @@
       <c r="G373" s="20"/>
       <c r="H373" s="20"/>
       <c r="I373" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J373" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K373" s="22"/>
@@ -10581,11 +10625,11 @@
       <c r="G374" s="20"/>
       <c r="H374" s="20"/>
       <c r="I374" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J374" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K374" s="22"/>
@@ -10603,11 +10647,11 @@
       <c r="G375" s="20"/>
       <c r="H375" s="20"/>
       <c r="I375" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J375" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K375" s="22"/>
@@ -10625,11 +10669,11 @@
       <c r="G376" s="20"/>
       <c r="H376" s="20"/>
       <c r="I376" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J376" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K376" s="22"/>
@@ -10647,11 +10691,11 @@
       <c r="G377" s="20"/>
       <c r="H377" s="20"/>
       <c r="I377" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J377" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K377" s="22"/>
@@ -10669,11 +10713,11 @@
       <c r="G378" s="20"/>
       <c r="H378" s="20"/>
       <c r="I378" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J378" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K378" s="22"/>
@@ -10691,11 +10735,11 @@
       <c r="G379" s="20"/>
       <c r="H379" s="20"/>
       <c r="I379" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J379" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K379" s="22"/>
@@ -10713,11 +10757,11 @@
       <c r="G380" s="20"/>
       <c r="H380" s="20"/>
       <c r="I380" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J380" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K380" s="22"/>
@@ -10735,11 +10779,11 @@
       <c r="G381" s="20"/>
       <c r="H381" s="20"/>
       <c r="I381" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J381" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K381" s="22"/>
@@ -10757,11 +10801,11 @@
       <c r="G382" s="20"/>
       <c r="H382" s="20"/>
       <c r="I382" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J382" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K382" s="22"/>
@@ -10779,11 +10823,11 @@
       <c r="G383" s="20"/>
       <c r="H383" s="20"/>
       <c r="I383" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J383" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K383" s="22"/>
@@ -10801,11 +10845,11 @@
       <c r="G384" s="20"/>
       <c r="H384" s="20"/>
       <c r="I384" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J384" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K384" s="22"/>
@@ -10823,11 +10867,11 @@
       <c r="G385" s="20"/>
       <c r="H385" s="20"/>
       <c r="I385" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J385" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K385" s="22"/>
@@ -10845,11 +10889,11 @@
       <c r="G386" s="20"/>
       <c r="H386" s="20"/>
       <c r="I386" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J386" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K386" s="22"/>
@@ -10867,11 +10911,11 @@
       <c r="G387" s="20"/>
       <c r="H387" s="20"/>
       <c r="I387" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J387" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K387" s="22"/>
@@ -10889,11 +10933,11 @@
       <c r="G388" s="20"/>
       <c r="H388" s="20"/>
       <c r="I388" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J388" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K388" s="22"/>
@@ -10911,11 +10955,11 @@
       <c r="G389" s="20"/>
       <c r="H389" s="20"/>
       <c r="I389" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J389" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K389" s="22"/>
@@ -10933,11 +10977,11 @@
       <c r="G390" s="20"/>
       <c r="H390" s="20"/>
       <c r="I390" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J390" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K390" s="22"/>
@@ -10955,11 +10999,11 @@
       <c r="G391" s="20"/>
       <c r="H391" s="20"/>
       <c r="I391" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J391" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K391" s="22"/>
@@ -10977,11 +11021,11 @@
       <c r="G392" s="20"/>
       <c r="H392" s="20"/>
       <c r="I392" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J392" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K392" s="22"/>
@@ -10999,11 +11043,11 @@
       <c r="G393" s="20"/>
       <c r="H393" s="20"/>
       <c r="I393" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J393" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K393" s="22"/>
@@ -11021,11 +11065,11 @@
       <c r="G394" s="20"/>
       <c r="H394" s="20"/>
       <c r="I394" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J394" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K394" s="22"/>
@@ -11043,11 +11087,11 @@
       <c r="G395" s="20"/>
       <c r="H395" s="20"/>
       <c r="I395" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J395" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K395" s="22"/>
@@ -11065,11 +11109,11 @@
       <c r="G396" s="20"/>
       <c r="H396" s="20"/>
       <c r="I396" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J396" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K396" s="22"/>
@@ -11087,11 +11131,11 @@
       <c r="G397" s="20"/>
       <c r="H397" s="20"/>
       <c r="I397" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J397" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K397" s="22"/>
@@ -11109,11 +11153,11 @@
       <c r="G398" s="20"/>
       <c r="H398" s="20"/>
       <c r="I398" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J398" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K398" s="22"/>
@@ -11131,11 +11175,11 @@
       <c r="G399" s="20"/>
       <c r="H399" s="20"/>
       <c r="I399" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J399" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K399" s="22"/>
@@ -11153,11 +11197,11 @@
       <c r="G400" s="20"/>
       <c r="H400" s="20"/>
       <c r="I400" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J400" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K400" s="22"/>
@@ -11175,11 +11219,11 @@
       <c r="G401" s="20"/>
       <c r="H401" s="20"/>
       <c r="I401" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J401" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K401" s="22"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -32,10 +32,10 @@
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
+    <t>Registration No.:</t>
   </si>
   <si>
-    <t>Registration No.:</t>
+    <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
   </si>
   <si>
     <t>4. COLUMN GUIDE</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
+    <t>Month:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
-    <t>Course / Section:</t>
+    <t>August</t>
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>Month:</t>
-  </si>
-  <si>
-    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -220,7 +220,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -236,13 +236,13 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF595959"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -252,13 +252,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <b/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -300,6 +300,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -449,8 +454,8 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,7 +702,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -707,7 +712,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
@@ -715,12 +720,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
+      <c r="A6" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
@@ -728,22 +733,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
@@ -751,17 +756,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
+      <c r="A15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
@@ -769,104 +774,104 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>30</v>
+      <c r="A31" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>32</v>
+      <c r="A34" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>34</v>
+      <c r="A35" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1856,21 +1861,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="6" t="s">
-        <v>15</v>
+      <c r="E2" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1882,19 +1887,19 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>33</v>
+      <c r="A3" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -2957,28 +2962,28 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="27">
+      <c r="A28" s="19">
         <v>46276.0</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="20">
         <v>360.0</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="20">
         <v>20.0</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="20">
         <v>120.0</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="20">
         <v>100.0</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="20">
         <v>300.0</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="20">
         <v>6.0</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="20">
         <v>150.0</v>
       </c>
       <c r="I28" s="21">
@@ -2989,42 +2994,42 @@
         <f t="shared" si="4"/>
         <v>390</v>
       </c>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="L28" s="29" t="s">
+      <c r="L28" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="N28" s="30" t="s">
+      <c r="N28" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="27">
+      <c r="A29" s="19">
         <v>46277.0</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="20">
         <v>360.0</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="20">
         <v>25.0</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="20">
         <v>100.0</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="20">
         <v>100.0</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="20">
         <v>0.0</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="20">
         <v>0.0</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="20">
         <v>200.0</v>
       </c>
       <c r="I29" s="21">
@@ -3035,39 +3040,64 @@
         <f t="shared" si="4"/>
         <v>655</v>
       </c>
-      <c r="K29" s="29" t="s">
+      <c r="K29" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="L29" s="29" t="s">
+      <c r="L29" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="M29" s="29" t="s">
+      <c r="M29" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="N29" s="30" t="s">
+      <c r="N29" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J30" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
+      <c r="A30" s="27">
+        <v>46278.0</v>
+      </c>
+      <c r="B30" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C30" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="D30" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E30" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F30" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I30" s="21">
+        <f t="shared" si="3"/>
+        <v>800</v>
+      </c>
+      <c r="J30" s="21">
+        <f t="shared" si="4"/>
+        <v>640</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -32,10 +32,10 @@
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
   </si>
   <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
@@ -98,31 +98,31 @@
     <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
   </si>
   <si>
     <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
   </si>
   <si>
-    <t>Course / Section:</t>
+    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
-    <t>MCA</t>
+    <t>Month:</t>
   </si>
   <si>
-    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
+    <t>August</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
-    <t>Month:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
-  </si>
-  <si>
-    <t>August</t>
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
@@ -220,7 +220,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -252,13 +252,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <b/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -300,11 +300,6 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -454,8 +449,8 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -712,7 +707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
@@ -720,12 +715,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
+      <c r="A6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
@@ -733,40 +728,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>13</v>
+      <c r="A14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
@@ -774,104 +769,104 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>28</v>
+      <c r="A29" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>29</v>
+      <c r="A30" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
-        <v>35</v>
+      <c r="A34" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1866,16 +1861,16 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="5" t="s">
-        <v>14</v>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1887,19 +1882,19 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>30</v>
+      <c r="A3" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -3054,28 +3049,28 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="27">
+      <c r="A30" s="19">
         <v>46278.0</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="20">
         <v>360.0</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="20">
         <v>20.0</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="20">
         <v>100.0</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="20">
         <v>120.0</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="20">
         <v>0.0</v>
       </c>
-      <c r="G30" s="28">
+      <c r="G30" s="20">
         <v>0.0</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="20">
         <v>200.0</v>
       </c>
       <c r="I30" s="21">
@@ -3086,40 +3081,64 @@
         <f t="shared" si="4"/>
         <v>640</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L30" s="29" t="s">
+      <c r="L30" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="29" t="s">
+      <c r="M30" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N30" s="30" t="s">
+      <c r="N30" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="19"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="23"/>
+      <c r="A31" s="27">
+        <v>46279.0</v>
+      </c>
+      <c r="B31" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C31" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="D31" s="28">
+        <v>110.0</v>
+      </c>
+      <c r="E31" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F31" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="G31" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="H31" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I31" s="21">
+        <f t="shared" si="3"/>
+        <v>1100</v>
+      </c>
+      <c r="J31" s="21">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="K31" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,30 +12,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
-    <t>Daily Activity Tracker — Instructions</t>
+    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
+    <t>1. FILE NAME</t>
   </si>
   <si>
     <t>Name:</t>
   </si>
   <si>
-    <t>1. FILE NAME</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -44,13 +41,13 @@
     <t xml:space="preserve">   Go to the 'Daily Log' tab. Fill in your Name and Registration Number at the top (yellow cells).</t>
   </si>
   <si>
+    <t>Shubham Patel</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Add one row per day. Cells shaded yellow are the only cells you should type into.</t>
   </si>
   <si>
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
@@ -98,12 +98,6 @@
     <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
   </si>
   <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
   </si>
   <si>
@@ -113,12 +107,6 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
-    <t>Month:</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -126,6 +114,18 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -236,12 +236,6 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -252,6 +246,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -259,13 +259,13 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -697,12 +697,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -710,8 +710,8 @@
       <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>5</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -723,13 +723,13 @@
       <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -746,41 +746,41 @@
       <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>13</v>
+      <c r="A13" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>16</v>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -825,42 +825,42 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>35</v>
+      <c r="A33" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7"/>
+      <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5"/>
@@ -1856,21 +1856,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
+      <c r="A2" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="6" t="s">
-        <v>12</v>
+      <c r="E2" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1882,19 +1882,19 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>28</v>
+      <c r="A3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -3095,28 +3095,28 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="27">
+      <c r="A31" s="19">
         <v>46279.0</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="20">
         <v>360.0</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="20">
         <v>10.0</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="20">
         <v>110.0</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="20">
         <v>120.0</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="20">
         <v>300.0</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="20">
         <v>6.0</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="20">
         <v>200.0</v>
       </c>
       <c r="I31" s="21">
@@ -3127,40 +3127,64 @@
         <f t="shared" si="4"/>
         <v>340</v>
       </c>
-      <c r="K31" s="29" t="s">
+      <c r="K31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L31" s="29" t="s">
+      <c r="L31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M31" s="29" t="s">
+      <c r="M31" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N31" s="30" t="s">
+      <c r="N31" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="19"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J32" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="23"/>
+      <c r="A32" s="27">
+        <v>46280.0</v>
+      </c>
+      <c r="B32" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C32" s="28">
+        <v>15.0</v>
+      </c>
+      <c r="D32" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E32" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F32" s="28">
+        <v>350.0</v>
+      </c>
+      <c r="G32" s="28">
+        <v>7.0</v>
+      </c>
+      <c r="H32" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I32" s="21">
+        <f t="shared" si="3"/>
+        <v>1065</v>
+      </c>
+      <c r="J32" s="21">
+        <f t="shared" si="4"/>
+        <v>375</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -20,16 +20,13 @@
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
+    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
+  </si>
+  <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
-    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
-  </si>
-  <si>
     <t>1. FILE NAME</t>
-  </si>
-  <si>
-    <t>Name:</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
@@ -39,9 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Go to the 'Daily Log' tab. Fill in your Name and Registration Number at the top (yellow cells).</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Add one row per day. Cells shaded yellow are the only cells you should type into.</t>
@@ -59,6 +53,9 @@
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t>4. COLUMN GUIDE</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
   </si>
   <si>
@@ -81,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Class (min)         - time spent in scheduled lectures/labs</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -211,6 +211,9 @@
   <si>
     <t>Stressed</t>
   </si>
+  <si>
+    <t>today is studying oops and then solving some question</t>
+  </si>
 </sst>
 </file>
 
@@ -246,12 +249,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -259,6 +256,12 @@
     <font>
       <b/>
       <sz val="11.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
@@ -703,170 +706,170 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+    <row r="16">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1856,21 +1859,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
+      <c r="A1" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -3141,28 +3144,28 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="27">
+      <c r="A32" s="19">
         <v>46280.0</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="20">
         <v>360.0</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="20">
         <v>15.0</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="20">
         <v>100.0</v>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="20">
         <v>60.0</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="20">
         <v>350.0</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="20">
         <v>7.0</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="20">
         <v>180.0</v>
       </c>
       <c r="I32" s="21">
@@ -3173,40 +3176,64 @@
         <f t="shared" si="4"/>
         <v>375</v>
       </c>
-      <c r="K32" s="29" t="s">
+      <c r="K32" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="L32" s="29" t="s">
+      <c r="L32" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M32" s="29" t="s">
+      <c r="M32" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N32" s="30" t="s">
+      <c r="N32" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="19"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="23"/>
+      <c r="A33" s="27">
+        <v>46281.0</v>
+      </c>
+      <c r="B33" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C33" s="28">
+        <v>15.0</v>
+      </c>
+      <c r="D33" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E33" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F33" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="G33" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="H33" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I33" s="21">
+        <f t="shared" si="3"/>
+        <v>1045</v>
+      </c>
+      <c r="J33" s="21">
+        <f t="shared" si="4"/>
+        <v>395</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="30" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -23,13 +26,16 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>Name:</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -53,13 +59,13 @@
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t>4. COLUMN GUIDE</t>
   </si>
   <si>
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
@@ -75,9 +81,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Class (min)         - time spent in scheduled lectures/labs</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
@@ -110,16 +113,13 @@
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t>Course / Section:</t>
   </si>
   <si>
     <t>MCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>Month:</t>
@@ -214,6 +214,9 @@
   <si>
     <t>today is studying oops and then solving some question</t>
   </si>
+  <si>
+    <t xml:space="preserve">today i preparing for SQL CA </t>
+  </si>
 </sst>
 </file>
 
@@ -239,6 +242,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -256,19 +265,13 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -700,176 +703,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
+      <c r="A5" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
+      <c r="A6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
+      <c r="A8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
+      <c r="A9" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
+      <c r="A10" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
+      <c r="A11" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>10</v>
+      <c r="A13" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
+      <c r="A14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>12</v>
+      <c r="A15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>14</v>
+      <c r="A17" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
+      <c r="A18" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
+      <c r="A19" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
+      <c r="A20" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
+      <c r="A21" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
+      <c r="A22" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
+      <c r="A23" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>22</v>
+      <c r="A24" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>23</v>
+      <c r="A25" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>24</v>
+      <c r="A26" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>25</v>
+      <c r="A27" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>26</v>
+      <c r="A28" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
+      <c r="A29" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>28</v>
+      <c r="A30" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>29</v>
+      <c r="A31" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>30</v>
+      <c r="A33" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>31</v>
+      <c r="A34" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>32</v>
+      <c r="A35" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1859,21 +1862,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>3</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
+      <c r="A2" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>33</v>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1885,15 +1888,15 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3190,28 +3193,28 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="27">
+      <c r="A33" s="19">
         <v>46281.0</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="20">
         <v>360.0</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="20">
         <v>15.0</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="20">
         <v>100.0</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="20">
         <v>120.0</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="20">
         <v>300.0</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="20">
         <v>6.0</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="20">
         <v>150.0</v>
       </c>
       <c r="I33" s="21">
@@ -3222,40 +3225,64 @@
         <f t="shared" si="4"/>
         <v>395</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K33" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="29" t="s">
+      <c r="L33" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M33" s="29" t="s">
+      <c r="M33" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N33" s="30" t="s">
+      <c r="N33" s="23" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J34" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="23"/>
+      <c r="A34" s="27">
+        <v>46282.0</v>
+      </c>
+      <c r="B34" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C34" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E34" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F34" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="G34" s="28">
+        <v>3.0</v>
+      </c>
+      <c r="H34" s="28">
+        <v>140.0</v>
+      </c>
+      <c r="I34" s="21">
+        <f t="shared" si="3"/>
+        <v>870</v>
+      </c>
+      <c r="J34" s="21">
+        <f t="shared" si="4"/>
+        <v>570</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="30" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,12 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -26,16 +23,10 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -63,9 +54,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
@@ -113,13 +101,25 @@
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
+  <si>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t>Course / Section:</t>
   </si>
   <si>
     <t>MCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>Month:</t>
@@ -217,6 +217,9 @@
   <si>
     <t xml:space="preserve">today i preparing for SQL CA </t>
   </si>
+  <si>
+    <t>today i preaparing for CA</t>
+  </si>
 </sst>
 </file>
 
@@ -242,12 +245,6 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -265,13 +262,19 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -703,176 +706,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="4">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+    <row r="12">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="16">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1862,21 +1865,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
+      <c r="A2" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
+      <c r="E2" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1888,15 +1891,15 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>33</v>
+      <c r="A3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3239,28 +3242,28 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="27">
+      <c r="A34" s="19">
         <v>46282.0</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="20">
         <v>360.0</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="20">
         <v>0.0</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="20">
         <v>100.0</v>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="20">
         <v>120.0</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="20">
         <v>150.0</v>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="20">
         <v>3.0</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="20">
         <v>140.0</v>
       </c>
       <c r="I34" s="21">
@@ -3271,40 +3274,64 @@
         <f t="shared" si="4"/>
         <v>570</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K34" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L34" s="29" t="s">
+      <c r="L34" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M34" s="29" t="s">
+      <c r="M34" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N34" s="30" t="s">
+      <c r="N34" s="23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="23"/>
+      <c r="A35" s="27">
+        <v>46283.0</v>
+      </c>
+      <c r="B35" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C35" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="D35" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E35" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="F35" s="28">
+        <v>250.0</v>
+      </c>
+      <c r="G35" s="28">
+        <v>5.0</v>
+      </c>
+      <c r="H35" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I35" s="21">
+        <f t="shared" si="3"/>
+        <v>970</v>
+      </c>
+      <c r="J35" s="21">
+        <f t="shared" si="4"/>
+        <v>470</v>
+      </c>
+      <c r="K35" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="30" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
@@ -27,6 +30,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+  </si>
+  <si>
+    <t>Name:</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -39,6 +45,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
@@ -74,6 +83,9 @@
     <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
   </si>
   <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
   </si>
   <si>
@@ -102,18 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
-  </si>
-  <si>
-    <t>Name:</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -220,6 +220,9 @@
   <si>
     <t>today i preaparing for CA</t>
   </si>
+  <si>
+    <t>today i attend CA Analytical</t>
+  </si>
 </sst>
 </file>
 
@@ -255,6 +258,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -262,12 +271,6 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
@@ -712,170 +715,170 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
+      <c r="A6" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
+      <c r="A9" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
+      <c r="A10" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
+      <c r="A11" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
+      <c r="A13" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>10</v>
+      <c r="A14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
+      <c r="A15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>12</v>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>13</v>
+      <c r="A18" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>14</v>
+      <c r="A19" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>15</v>
+      <c r="A20" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>16</v>
+      <c r="A21" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>17</v>
+      <c r="A22" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>18</v>
+      <c r="A23" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
+      <c r="A24" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>20</v>
+      <c r="A25" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
+      <c r="A26" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>22</v>
+      <c r="A27" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>23</v>
+      <c r="A28" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
+      <c r="A29" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>25</v>
+      <c r="A30" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>26</v>
+      <c r="A31" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>27</v>
+      <c r="A33" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>28</v>
+      <c r="A34" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>29</v>
+      <c r="A35" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1865,21 +1868,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>30</v>
+      <c r="A1" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -3288,28 +3291,28 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="27">
+      <c r="A35" s="19">
         <v>46283.0</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="20">
         <v>360.0</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="20">
         <v>10.0</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="20">
         <v>100.0</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="20">
         <v>100.0</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="20">
         <v>250.0</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="20">
         <v>5.0</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="20">
         <v>150.0</v>
       </c>
       <c r="I35" s="21">
@@ -3320,40 +3323,64 @@
         <f t="shared" si="4"/>
         <v>470</v>
       </c>
-      <c r="K35" s="29" t="s">
+      <c r="K35" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L35" s="29" t="s">
+      <c r="L35" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M35" s="29" t="s">
+      <c r="M35" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N35" s="30" t="s">
+      <c r="N35" s="23" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J36" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="23"/>
+      <c r="A36" s="27">
+        <v>46284.0</v>
+      </c>
+      <c r="B36" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C36" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E36" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F36" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I36" s="21">
+        <f t="shared" si="3"/>
+        <v>700</v>
+      </c>
+      <c r="J36" s="21">
+        <f t="shared" si="4"/>
+        <v>740</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" s="30" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
+  <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -20,19 +23,19 @@
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
+    <t>Name:</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -45,9 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
@@ -81,9 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
@@ -223,6 +223,9 @@
   <si>
     <t>today i attend CA Analytical</t>
   </si>
+  <si>
+    <t>today i study in C++</t>
+  </si>
 </sst>
 </file>
 
@@ -248,6 +251,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -258,12 +267,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -271,13 +274,13 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -705,16 +708,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -722,43 +725,43 @@
       <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
+      <c r="A5" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
+      <c r="A8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -776,7 +779,7 @@
       <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -787,32 +790,32 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -854,7 +857,7 @@
       <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -872,7 +875,7 @@
       <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5"/>
@@ -1868,21 +1871,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>23</v>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1894,7 +1897,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1902,7 +1905,7 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3337,28 +3340,28 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="27">
+      <c r="A36" s="19">
         <v>46284.0</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="20">
         <v>360.0</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="20">
         <v>0.0</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="20">
         <v>100.0</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="20">
         <v>60.0</v>
       </c>
-      <c r="F36" s="28">
+      <c r="F36" s="20">
         <v>0.0</v>
       </c>
-      <c r="G36" s="28">
+      <c r="G36" s="20">
         <v>0.0</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="20">
         <v>180.0</v>
       </c>
       <c r="I36" s="21">
@@ -3369,40 +3372,64 @@
         <f t="shared" si="4"/>
         <v>740</v>
       </c>
-      <c r="K36" s="29" t="s">
+      <c r="K36" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L36" s="29" t="s">
+      <c r="L36" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M36" s="29" t="s">
+      <c r="M36" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N36" s="30" t="s">
+      <c r="N36" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="23"/>
+      <c r="A37" s="27">
+        <v>46285.0</v>
+      </c>
+      <c r="B37" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C37" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="D37" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E37" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F37" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I37" s="21">
+        <f t="shared" si="3"/>
+        <v>740</v>
+      </c>
+      <c r="J37" s="21">
+        <f t="shared" si="4"/>
+        <v>700</v>
+      </c>
+      <c r="K37" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="30" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,30 +12,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="72">
+  <si>
+    <t>My Data, My Code</t>
+  </si>
   <si>
     <t>My Data, My Code — Daily Log</t>
-  </si>
-  <si>
-    <t>My Data, My Code</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
+    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -65,19 +68,28 @@
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
   </si>
   <si>
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
   </si>
   <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Coding (min)        - programming / lab / project work</t>
+  </si>
+  <si>
+    <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
   <si>
     <t xml:space="preserve">   Class (min)         - time spent in scheduled lectures/labs</t>
@@ -86,55 +98,25 @@
     <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
   </si>
   <si>
+    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
   </si>
   <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
   </si>
   <si>
-    <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
+    <t>Sleep (min)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
-  </si>
-  <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>Month:</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Sleep (min)</t>
+    <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
   </si>
   <si>
     <t>Fitness (min)</t>
@@ -152,7 +134,13 @@
     <t>Classes Attended</t>
   </si>
   <si>
+    <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
+  </si>
+  <si>
     <t>Other Activities (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
   </si>
   <si>
     <t>Total Tracked (min)</t>
@@ -164,13 +152,25 @@
     <t>Day's Feeling</t>
   </si>
   <si>
+    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
+  </si>
+  <si>
     <t>Satisfaction Level</t>
   </si>
   <si>
     <t>Energy Level</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>Good</t>
@@ -226,6 +226,9 @@
   <si>
     <t>today i study in C++</t>
   </si>
+  <si>
+    <t>today i studying in english and networking</t>
+  </si>
 </sst>
 </file>
 
@@ -261,6 +264,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF595959"/>
@@ -272,21 +281,15 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font/>
     <font>
@@ -407,8 +410,8 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
@@ -431,40 +434,40 @@
     <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -708,7 +711,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
@@ -717,171 +720,171 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
+      <c r="A3" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>5</v>
+      <c r="A5" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
+      <c r="A8" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
+      <c r="A9" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>10</v>
+      <c r="A10" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>11</v>
+      <c r="A11" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>12</v>
+      <c r="A13" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
+      <c r="A14" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
+      <c r="A15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>15</v>
+      <c r="A17" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>16</v>
+      <c r="A18" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>20</v>
+      <c r="A21" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>21</v>
+      <c r="A22" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>22</v>
+      <c r="A23" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>23</v>
+      <c r="A24" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>24</v>
+      <c r="A25" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>25</v>
+      <c r="A26" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>26</v>
+      <c r="A27" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>27</v>
+      <c r="A28" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>28</v>
+      <c r="A29" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>29</v>
+      <c r="A30" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>30</v>
+      <c r="A31" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>31</v>
+      <c r="A33" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>32</v>
+      <c r="A34" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>33</v>
+      <c r="A35" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7"/>
+      <c r="A37" s="8"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1872,22 +1875,22 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>6</v>
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="7">
         <v>1.2602441E7</v>
       </c>
       <c r="G2" s="10"/>
@@ -1897,69 +1900,69 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>37</v>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="H5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="I5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="J5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="K5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="13" t="s">
+      <c r="L5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="M5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="13" t="s">
+      <c r="N5" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -3386,28 +3389,28 @@
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="27">
+      <c r="A37" s="19">
         <v>46285.0</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="20">
         <v>360.0</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="20">
         <v>10.0</v>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="20">
         <v>100.0</v>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="20">
         <v>120.0</v>
       </c>
-      <c r="F37" s="28">
+      <c r="F37" s="20">
         <v>0.0</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="20">
         <v>0.0</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="20">
         <v>150.0</v>
       </c>
       <c r="I37" s="21">
@@ -3418,40 +3421,64 @@
         <f t="shared" si="4"/>
         <v>700</v>
       </c>
-      <c r="K37" s="29" t="s">
+      <c r="K37" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="29" t="s">
+      <c r="L37" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M37" s="29" t="s">
+      <c r="M37" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N37" s="30" t="s">
+      <c r="N37" s="23" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J38" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="23"/>
+      <c r="A38" s="27">
+        <v>46286.0</v>
+      </c>
+      <c r="B38" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C38" s="28">
+        <v>12.0</v>
+      </c>
+      <c r="D38" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="E38" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="F38" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="G38" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="H38" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I38" s="21">
+        <f t="shared" si="3"/>
+        <v>778</v>
+      </c>
+      <c r="J38" s="21">
+        <f t="shared" si="4"/>
+        <v>662</v>
+      </c>
+      <c r="K38" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="30" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,33 +12,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -68,22 +56,70 @@
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
   </si>
   <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
   </si>
   <si>
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
   </si>
   <si>
+    <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Coding (min)        - programming / lab / project work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Class (min)         - time spent in scheduled lectures/labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
+  </si>
+  <si>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
+  </si>
+  <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
+  </si>
+  <si>
     <t>Course / Section:</t>
   </si>
   <si>
-    <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
-  </si>
-  <si>
     <t>MCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Coding (min)        - programming / lab / project work</t>
   </si>
   <si>
     <t>Month:</t>
@@ -92,31 +128,13 @@
     <t>August</t>
   </si>
   <si>
-    <t xml:space="preserve">   Class (min)         - time spent in scheduled lectures/labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Classes Attended    - number of class sessions attended that day</t>
-  </si>
-  <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
-  </si>
-  <si>
     <t>Sleep (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
   </si>
   <si>
     <t>Fitness (min)</t>
@@ -134,13 +152,7 @@
     <t>Classes Attended</t>
   </si>
   <si>
-    <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
-  </si>
-  <si>
     <t>Other Activities (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Energy Level        - pick from the dropdown: High / Medium / Low</t>
   </si>
   <si>
     <t>Total Tracked (min)</t>
@@ -152,25 +164,13 @@
     <t>Day's Feeling</t>
   </si>
   <si>
-    <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
-  </si>
-  <si>
     <t>Satisfaction Level</t>
   </si>
   <si>
     <t>Energy Level</t>
   </si>
   <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>Good</t>
@@ -229,6 +229,9 @@
   <si>
     <t>today i studying in english and networking</t>
   </si>
+  <si>
+    <t>i study english and networking</t>
+  </si>
 </sst>
 </file>
 
@@ -254,19 +257,7 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF595959"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -281,15 +272,27 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
+      <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font/>
     <font>
@@ -410,8 +413,8 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
@@ -434,40 +437,40 @@
     <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -715,176 +718,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="4">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+    <row r="7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="16">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1874,23 +1877,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
+      <c r="A2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="8">
         <v>1.2602441E7</v>
       </c>
       <c r="G2" s="10"/>
@@ -1900,69 +1903,69 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
+      <c r="A3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -3435,28 +3438,28 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="27">
+      <c r="A38" s="19">
         <v>46286.0</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="20">
         <v>360.0</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="20">
         <v>12.0</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="20">
         <v>120.0</v>
       </c>
-      <c r="E38" s="28">
+      <c r="E38" s="20">
         <v>100.0</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="20">
         <v>6.0</v>
       </c>
-      <c r="G38" s="28">
+      <c r="G38" s="20">
         <v>300.0</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="20">
         <v>180.0</v>
       </c>
       <c r="I38" s="21">
@@ -3467,40 +3470,64 @@
         <f t="shared" si="4"/>
         <v>662</v>
       </c>
-      <c r="K38" s="29" t="s">
+      <c r="K38" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L38" s="29" t="s">
+      <c r="L38" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M38" s="29" t="s">
+      <c r="M38" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N38" s="30" t="s">
+      <c r="N38" s="23" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="23"/>
+      <c r="A39" s="27">
+        <v>46287.0</v>
+      </c>
+      <c r="B39" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C39" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="D39" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="E39" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F39" s="28">
+        <v>350.0</v>
+      </c>
+      <c r="G39" s="28">
+        <v>7.0</v>
+      </c>
+      <c r="H39" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I39" s="21">
+        <f t="shared" si="3"/>
+        <v>1080</v>
+      </c>
+      <c r="J39" s="21">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="30" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -23,7 +26,13 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t>1. FILE NAME</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
@@ -56,9 +65,6 @@
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Coding (min)        - programming / lab / project work</t>
@@ -89,9 +98,6 @@
     <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Satisfaction Level  - pick from the dropdown: Very Satisfied / Satisfied / Neutral / Unsatisfied / Very Unsatisfied</t>
   </si>
   <si>
@@ -104,16 +110,10 @@
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -257,6 +257,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -264,6 +270,12 @@
       <i/>
       <sz val="10.0"/>
       <color rgb="FF595959"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -275,18 +287,6 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -461,10 +461,10 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -718,176 +718,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
+      <c r="A6" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
+      <c r="A8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
+      <c r="A10" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
+      <c r="A11" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
+      <c r="A13" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>10</v>
+      <c r="A14" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
+      <c r="A15" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>12</v>
+      <c r="A17" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>13</v>
+      <c r="A18" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>15</v>
+      <c r="A19" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>16</v>
+      <c r="A20" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>17</v>
+      <c r="A21" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
+      <c r="A22" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>19</v>
+      <c r="A23" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>20</v>
+      <c r="A24" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>21</v>
+      <c r="A25" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
+      <c r="A26" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>23</v>
+      <c r="A27" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>24</v>
+      <c r="A28" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>26</v>
+      <c r="A29" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>27</v>
+      <c r="A30" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>28</v>
+      <c r="A31" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>29</v>
+      <c r="A33" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>31</v>
+      <c r="A34" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>32</v>
+      <c r="A35" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1877,21 +1877,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>25</v>
+      <c r="A2" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>33</v>
+      <c r="E2" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3453,22 +3453,22 @@
       <c r="E38" s="20">
         <v>100.0</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="27">
+        <v>300.0</v>
+      </c>
+      <c r="G38" s="27">
         <v>6.0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>300.0</v>
       </c>
       <c r="H38" s="20">
         <v>180.0</v>
       </c>
       <c r="I38" s="21">
         <f t="shared" si="3"/>
-        <v>778</v>
+        <v>1072</v>
       </c>
       <c r="J38" s="21">
         <f t="shared" si="4"/>
-        <v>662</v>
+        <v>368</v>
       </c>
       <c r="K38" s="22" t="s">
         <v>58</v>
@@ -3484,28 +3484,28 @@
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="27">
+      <c r="A39" s="19">
         <v>46287.0</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="20">
         <v>360.0</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="20">
         <v>10.0</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="20">
         <v>120.0</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="20">
         <v>60.0</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="20">
         <v>350.0</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="20">
         <v>7.0</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="20">
         <v>180.0</v>
       </c>
       <c r="I39" s="21">
@@ -3516,40 +3516,64 @@
         <f t="shared" si="4"/>
         <v>360</v>
       </c>
-      <c r="K39" s="29" t="s">
+      <c r="K39" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L39" s="29" t="s">
+      <c r="L39" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M39" s="29" t="s">
+      <c r="M39" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N39" s="30" t="s">
+      <c r="N39" s="23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J40" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="23"/>
+      <c r="A40" s="28">
+        <v>46288.0</v>
+      </c>
+      <c r="B40" s="27">
+        <v>300.0</v>
+      </c>
+      <c r="C40" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="D40" s="27">
+        <v>80.0</v>
+      </c>
+      <c r="E40" s="27">
+        <v>90.0</v>
+      </c>
+      <c r="F40" s="27">
+        <v>300.0</v>
+      </c>
+      <c r="G40" s="27">
+        <v>6.0</v>
+      </c>
+      <c r="H40" s="27">
+        <v>140.0</v>
+      </c>
+      <c r="I40" s="21">
+        <f t="shared" si="3"/>
+        <v>910</v>
+      </c>
+      <c r="J40" s="21">
+        <f t="shared" si="4"/>
+        <v>530</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="30" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,12 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -26,13 +23,7 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t>1. FILE NAME</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
@@ -56,6 +47,9 @@
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
   </si>
   <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
   </si>
   <si>
@@ -74,9 +68,6 @@
     <t xml:space="preserve">   Study (min)         - academic study/reading time (non-coding)</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Coding (min)        - programming / lab / project work</t>
   </si>
   <si>
@@ -87,6 +78,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
+  </si>
+  <si>
+    <t>Name:</t>
   </si>
   <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
@@ -107,6 +101,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>Shubham Patel</t>
+  </si>
+  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -232,6 +232,9 @@
   <si>
     <t>i study english and networking</t>
   </si>
+  <si>
+    <t>today i study oops</t>
+  </si>
 </sst>
 </file>
 
@@ -257,12 +260,6 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -270,12 +267,6 @@
       <i/>
       <sz val="10.0"/>
       <color rgb="FF595959"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -287,6 +278,18 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -461,10 +464,10 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -718,176 +721,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="4">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+    <row r="12">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+    <row r="16">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="7" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1877,21 +1880,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>4</v>
+      <c r="A2" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="5" t="s">
-        <v>20</v>
+      <c r="E2" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1903,7 +1906,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1911,7 +1914,7 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3453,10 +3456,10 @@
       <c r="E38" s="20">
         <v>100.0</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="20">
         <v>300.0</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="20">
         <v>6.0</v>
       </c>
       <c r="H38" s="20">
@@ -3530,28 +3533,28 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="28">
+      <c r="A40" s="19">
         <v>46288.0</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="20">
         <v>300.0</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="20">
         <v>0.0</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="20">
         <v>80.0</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="20">
         <v>90.0</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="20">
         <v>300.0</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="20">
         <v>6.0</v>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="20">
         <v>140.0</v>
       </c>
       <c r="I40" s="21">
@@ -3562,40 +3565,64 @@
         <f t="shared" si="4"/>
         <v>530</v>
       </c>
-      <c r="K40" s="29" t="s">
+      <c r="K40" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L40" s="29" t="s">
+      <c r="L40" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M40" s="29" t="s">
+      <c r="M40" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N40" s="30" t="s">
+      <c r="N40" s="23" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="23"/>
+      <c r="A41" s="27">
+        <v>46289.0</v>
+      </c>
+      <c r="B41" s="28">
+        <v>330.0</v>
+      </c>
+      <c r="C41" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D41" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E41" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F41" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="G41" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="H41" s="28">
+        <v>170.0</v>
+      </c>
+      <c r="I41" s="21">
+        <f t="shared" si="3"/>
+        <v>820</v>
+      </c>
+      <c r="J41" s="21">
+        <f t="shared" si="4"/>
+        <v>620</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N41" s="30" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -24,6 +27,9 @@
   </si>
   <si>
     <t>1. FILE NAME</t>
+  </si>
+  <si>
+    <t>Name:</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
@@ -41,13 +47,13 @@
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
   </si>
   <si>
+    <t>Shubham Patel</t>
+  </si>
+  <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t xml:space="preserve">   Example: 2.5 hours of study = 150. 45 minutes of fitness = 45. 8 hours of sleep = 480.</t>
@@ -80,9 +86,6 @@
     <t xml:space="preserve">   Other Activities (min) - anything else worth tracking (chores, socializing, hobbies, etc.)</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
@@ -99,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
@@ -260,6 +260,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -277,12 +283,6 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
@@ -721,176 +721,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
+      <c r="A6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
+      <c r="A9" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
+      <c r="A10" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
+      <c r="A11" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
+      <c r="A13" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>10</v>
+      <c r="A14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>12</v>
+      <c r="A15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>13</v>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>14</v>
+      <c r="A18" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>15</v>
+      <c r="A19" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>16</v>
+      <c r="A20" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>17</v>
+      <c r="A21" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
+      <c r="A22" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>19</v>
+      <c r="A23" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>20</v>
+      <c r="A24" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>21</v>
+      <c r="A25" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>23</v>
+      <c r="A26" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>24</v>
+      <c r="A27" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>25</v>
+      <c r="A28" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>26</v>
+      <c r="A29" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>27</v>
+      <c r="A30" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>28</v>
+      <c r="A31" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1880,16 +1880,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>11</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -3579,28 +3579,28 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="27">
+      <c r="A41" s="19">
         <v>46289.0</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="20">
         <v>330.0</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="20">
         <v>0.0</v>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="20">
         <v>100.0</v>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="20">
         <v>120.0</v>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="20">
         <v>100.0</v>
       </c>
-      <c r="G41" s="28">
+      <c r="G41" s="20">
         <v>2.0</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="20">
         <v>170.0</v>
       </c>
       <c r="I41" s="21">
@@ -3611,40 +3611,64 @@
         <f t="shared" si="4"/>
         <v>620</v>
       </c>
-      <c r="K41" s="29" t="s">
+      <c r="K41" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="29" t="s">
+      <c r="L41" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="29" t="s">
+      <c r="M41" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="N41" s="30" t="s">
+      <c r="N41" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J42" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="23"/>
+      <c r="A42" s="27">
+        <v>46290.0</v>
+      </c>
+      <c r="B42" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C42" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D42" s="28">
+        <v>80.0</v>
+      </c>
+      <c r="E42" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="F42" s="28">
+        <v>250.0</v>
+      </c>
+      <c r="G42" s="28">
+        <v>5.0</v>
+      </c>
+      <c r="H42" s="28">
+        <v>140.0</v>
+      </c>
+      <c r="I42" s="21">
+        <f t="shared" si="3"/>
+        <v>980</v>
+      </c>
+      <c r="J42" s="21">
+        <f t="shared" si="4"/>
+        <v>460</v>
+      </c>
+      <c r="K42" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="30" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,24 +12,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="75">
+  <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>1. FILE NAME</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t>Registration No.:</t>
+  </si>
+  <si>
+    <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
@@ -45,9 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Do not edit the white/grey formula cells (Total Tracked, Free/Unaccounted) — they calculate automatically.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
@@ -111,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -235,6 +235,9 @@
   <si>
     <t>today i study oops</t>
   </si>
+  <si>
+    <t>today i work in python project</t>
+  </si>
 </sst>
 </file>
 
@@ -270,11 +273,23 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font/>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -286,18 +301,6 @@
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -415,11 +418,11 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -440,40 +443,40 @@
     <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,7 +720,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -726,171 +729,171 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
+      <c r="A3" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
+      <c r="A5" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
+      <c r="A6" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
+      <c r="A8" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
+      <c r="A9" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
+      <c r="A10" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
+      <c r="A11" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>12</v>
+      <c r="A13" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
+      <c r="A14" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
+      <c r="A15" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>15</v>
+      <c r="A17" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>16</v>
+      <c r="A18" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>17</v>
+      <c r="A19" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>18</v>
+      <c r="A20" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>19</v>
+      <c r="A21" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>20</v>
+      <c r="A22" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>21</v>
+      <c r="A23" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>22</v>
+      <c r="A24" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>23</v>
+      <c r="A25" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>24</v>
+      <c r="A26" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>25</v>
+      <c r="A27" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>26</v>
+      <c r="A28" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>27</v>
+      <c r="A29" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>28</v>
+      <c r="A30" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>29</v>
+      <c r="A31" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5"/>
+      <c r="A32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>30</v>
+      <c r="A33" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>31</v>
+      <c r="A34" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>32</v>
+      <c r="A35" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
+      <c r="A37" s="10"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5"/>
+      <c r="A38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5"/>
+      <c r="A39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1881,46 +1884,46 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6">
         <v>1.2602441E7</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="8"/>
       <c r="M2" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Fill an appropriate value for this cell based on the table context"")"),"=AI(""Fill an appropriate value for this cell based on the table context"")")</f>
         <v>=AI("Fill an appropriate value for this cell based on the table context")</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
@@ -3625,28 +3628,28 @@
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="27">
+      <c r="A42" s="19">
         <v>46290.0</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="20">
         <v>360.0</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="20">
         <v>0.0</v>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="20">
         <v>80.0</v>
       </c>
-      <c r="E42" s="28">
+      <c r="E42" s="20">
         <v>150.0</v>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="20">
         <v>250.0</v>
       </c>
-      <c r="G42" s="28">
+      <c r="G42" s="20">
         <v>5.0</v>
       </c>
-      <c r="H42" s="28">
+      <c r="H42" s="20">
         <v>140.0</v>
       </c>
       <c r="I42" s="21">
@@ -3657,40 +3660,64 @@
         <f t="shared" si="4"/>
         <v>460</v>
       </c>
-      <c r="K42" s="29" t="s">
+      <c r="K42" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L42" s="29" t="s">
+      <c r="L42" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M42" s="29" t="s">
+      <c r="M42" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N42" s="30" t="s">
+      <c r="N42" s="23" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="23"/>
+      <c r="A43" s="27">
+        <v>46291.0</v>
+      </c>
+      <c r="B43" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="C43" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="D43" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E43" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="F43" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="G43" s="28">
+        <v>3.0</v>
+      </c>
+      <c r="H43" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I43" s="21">
+        <f t="shared" si="3"/>
+        <v>920</v>
+      </c>
+      <c r="J43" s="21">
+        <f t="shared" si="4"/>
+        <v>520</v>
+      </c>
+      <c r="K43" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="30" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="78">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -20,19 +20,16 @@
     <t>My Data, My Code</t>
   </si>
   <si>
-    <t>Daily Activity Tracker — Instructions</t>
+    <t>Name:</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
     <t>Shubham Patel</t>
-  </si>
-  <si>
-    <t>Registration No.:</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
@@ -238,6 +238,15 @@
   <si>
     <t>today i work in python project</t>
   </si>
+  <si>
+    <t>i am travaling in train</t>
+  </si>
+  <si>
+    <t>i back in my home</t>
+  </si>
+  <si>
+    <t>i study in c++</t>
+  </si>
 </sst>
 </file>
 
@@ -256,14 +265,20 @@
     </font>
     <font>
       <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -273,23 +288,11 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -301,6 +304,12 @@
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font/>
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -418,11 +427,11 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -443,40 +452,40 @@
     <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="14" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -719,13 +728,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
+      <c r="A2" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -734,166 +743,166 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="s">
+    <row r="7">
+      <c r="A7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
+    <row r="9">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="s">
+    <row r="10">
+      <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="s">
+    <row r="11">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="s">
+    <row r="12">
+      <c r="A12" s="6"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="s">
+    <row r="14">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="s">
+    <row r="15">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="s">
+    <row r="16">
+      <c r="A16" s="6"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="s">
+    <row r="18">
+      <c r="A18" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="s">
+    <row r="19">
+      <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="s">
+    <row r="20">
+      <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="9"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="10"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="9"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="9"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1883,47 +1892,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="8">
         <v>1.2602441E7</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="10"/>
       <c r="M2" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Fill an appropriate value for this cell based on the table context"")"),"=AI(""Fill an appropriate value for this cell based on the table context"")")</f>
         <v>=AI("Fill an appropriate value for this cell based on the table context")</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
@@ -3674,28 +3683,28 @@
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="27">
+      <c r="A43" s="19">
         <v>46291.0</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="20">
         <v>300.0</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="20">
         <v>10.0</v>
       </c>
-      <c r="D43" s="28">
+      <c r="D43" s="20">
         <v>100.0</v>
       </c>
-      <c r="E43" s="28">
+      <c r="E43" s="20">
         <v>180.0</v>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="20">
         <v>150.0</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="20">
         <v>3.0</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="20">
         <v>180.0</v>
       </c>
       <c r="I43" s="21">
@@ -3706,84 +3715,154 @@
         <f t="shared" si="4"/>
         <v>520</v>
       </c>
-      <c r="K43" s="29" t="s">
+      <c r="K43" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L43" s="29" t="s">
+      <c r="L43" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M43" s="29" t="s">
+      <c r="M43" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="30" t="s">
+      <c r="N43" s="23" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J44" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="23"/>
+      <c r="A44" s="27">
+        <v>46295.0</v>
+      </c>
+      <c r="B44" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="C44" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D44" s="28">
+        <v>50.0</v>
+      </c>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G44" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H44" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I44" s="21">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="J44" s="21">
+        <f t="shared" si="4"/>
+        <v>890</v>
+      </c>
+      <c r="K44" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M44" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N44" s="30" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="23"/>
+      <c r="A45" s="27">
+        <v>46296.0</v>
+      </c>
+      <c r="B45" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D45" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="E45" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F45" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G45" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H45" s="28">
+        <v>180.0</v>
+      </c>
+      <c r="I45" s="21">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="J45" s="21">
+        <f t="shared" si="4"/>
+        <v>780</v>
+      </c>
+      <c r="K45" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="30" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J46" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="23"/>
+      <c r="A46" s="27">
+        <v>46297.0</v>
+      </c>
+      <c r="B46" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C46" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D46" s="28">
+        <v>100.0</v>
+      </c>
+      <c r="E46" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F46" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G46" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H46" s="28">
+        <v>200.0</v>
+      </c>
+      <c r="I46" s="21">
+        <f t="shared" si="3"/>
+        <v>780</v>
+      </c>
+      <c r="J46" s="21">
+        <f t="shared" si="4"/>
+        <v>660</v>
+      </c>
+      <c r="K46" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="30" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,24 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="78">
-  <si>
-    <t>My Data, My Code — Daily Log</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
-  </si>
-  <si>
-    <t>Name:</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
   </si>
   <si>
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
@@ -39,6 +30,9 @@
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t xml:space="preserve">   Go to the 'Daily Log' tab. Fill in your Name and Registration Number at the top (yellow cells).</t>
@@ -68,6 +62,9 @@
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
   </si>
   <si>
+    <t>Name:</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
   </si>
   <si>
@@ -89,10 +86,10 @@
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
   </si>
   <si>
-    <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
+    <t>Shubham Patel</t>
   </si>
   <si>
-    <t>Registration No.:</t>
+    <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
   </si>
   <si>
     <t xml:space="preserve">   Day's Feeling       - pick from the dropdown: Excellent / Good / Neutral / Low / Stressed</t>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
@@ -247,6 +247,9 @@
   <si>
     <t>i study in c++</t>
   </si>
+  <si>
+    <t>today i study in networking</t>
+  </si>
 </sst>
 </file>
 
@@ -265,20 +268,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18.0"/>
       <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -302,6 +293,18 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -728,181 +731,181 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="7">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="12">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+    <row r="16">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="7" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1892,21 +1895,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
+      <c r="A2" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="3" t="s">
-        <v>26</v>
+      <c r="E2" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1918,7 +1921,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1926,7 +1929,7 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -3729,26 +3732,26 @@
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="27">
+      <c r="A44" s="19">
         <v>46295.0</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="20">
         <v>300.0</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="20">
         <v>0.0</v>
       </c>
-      <c r="D44" s="28">
+      <c r="D44" s="20">
         <v>50.0</v>
       </c>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28">
+      <c r="E44" s="20"/>
+      <c r="F44" s="20">
         <v>0.0</v>
       </c>
-      <c r="G44" s="28">
+      <c r="G44" s="20">
         <v>0.0</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H44" s="20">
         <v>200.0</v>
       </c>
       <c r="I44" s="21">
@@ -3759,42 +3762,42 @@
         <f t="shared" si="4"/>
         <v>890</v>
       </c>
-      <c r="K44" s="29" t="s">
+      <c r="K44" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="L44" s="29" t="s">
+      <c r="L44" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="M44" s="29" t="s">
+      <c r="M44" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="N44" s="30" t="s">
+      <c r="N44" s="23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="27">
+      <c r="A45" s="19">
         <v>46296.0</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="20">
         <v>360.0</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="20">
         <v>0.0</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="20">
         <v>60.0</v>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="20">
         <v>60.0</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="20">
         <v>0.0</v>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="20">
         <v>0.0</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="20">
         <v>180.0</v>
       </c>
       <c r="I45" s="21">
@@ -3805,42 +3808,42 @@
         <f t="shared" si="4"/>
         <v>780</v>
       </c>
-      <c r="K45" s="29" t="s">
+      <c r="K45" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L45" s="29" t="s">
+      <c r="L45" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M45" s="29" t="s">
+      <c r="M45" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N45" s="30" t="s">
+      <c r="N45" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="27">
+      <c r="A46" s="19">
         <v>46297.0</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="20">
         <v>360.0</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="20">
         <v>0.0</v>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="20">
         <v>100.0</v>
       </c>
-      <c r="E46" s="28">
+      <c r="E46" s="20">
         <v>120.0</v>
       </c>
-      <c r="F46" s="28">
+      <c r="F46" s="20">
         <v>0.0</v>
       </c>
-      <c r="G46" s="28">
+      <c r="G46" s="20">
         <v>0.0</v>
       </c>
-      <c r="H46" s="28">
+      <c r="H46" s="20">
         <v>200.0</v>
       </c>
       <c r="I46" s="21">
@@ -3851,40 +3854,64 @@
         <f t="shared" si="4"/>
         <v>660</v>
       </c>
-      <c r="K46" s="29" t="s">
+      <c r="K46" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L46" s="29" t="s">
+      <c r="L46" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M46" s="29" t="s">
+      <c r="M46" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N46" s="30" t="s">
+      <c r="N46" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="23"/>
+      <c r="A47" s="27">
+        <v>46298.0</v>
+      </c>
+      <c r="B47" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="C47" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D47" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="E47" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F47" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G47" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H47" s="28">
+        <v>170.0</v>
+      </c>
+      <c r="I47" s="21">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="J47" s="21">
+        <f t="shared" si="4"/>
+        <v>790</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M47" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="30" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -23,16 +23,19 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
+    <t>My Data, My Code — Daily Log</t>
+  </si>
+  <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
   </si>
   <si>
-    <t>2. WHERE TO ENTER DATA</t>
+    <t>Name:</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>2. WHERE TO ENTER DATA</t>
   </si>
   <si>
     <t xml:space="preserve">   Go to the 'Daily Log' tab. Fill in your Name and Registration Number at the top (yellow cells).</t>
@@ -45,6 +48,9 @@
   </si>
   <si>
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
@@ -60,9 +66,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Sleep (min)        - total sleep duration</t>
-  </si>
-  <si>
-    <t>Name:</t>
   </si>
   <si>
     <t xml:space="preserve">   Fitness (min)       - workout / sport / walk / yoga time</t>
@@ -84,9 +87,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Total Tracked (min)  - auto-calculated sum of all the minute columns above</t>
-  </si>
-  <si>
-    <t>Shubham Patel</t>
   </si>
   <si>
     <t xml:space="preserve">   Free/Unaccounted (min) - auto-calculated as 1440 minus Total Tracked</t>
@@ -250,6 +250,9 @@
   <si>
     <t>today i study in networking</t>
   </si>
+  <si>
+    <t>today i study in python</t>
+  </si>
 </sst>
 </file>
 
@@ -291,13 +294,13 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="13.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
     </font>
@@ -479,10 +482,10 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -749,107 +752,107 @@
       <c r="A4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
+      <c r="A8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>10</v>
+      <c r="A13" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>13</v>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -881,7 +884,7 @@
       <c r="A32" s="4"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -899,7 +902,7 @@
       <c r="A36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4"/>
@@ -1895,16 +1898,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>6</v>
+      <c r="A1" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -3744,7 +3747,9 @@
       <c r="D44" s="20">
         <v>50.0</v>
       </c>
-      <c r="E44" s="20"/>
+      <c r="E44" s="27">
+        <v>100.0</v>
+      </c>
       <c r="F44" s="20">
         <v>0.0</v>
       </c>
@@ -3756,11 +3761,11 @@
       </c>
       <c r="I44" s="21">
         <f t="shared" si="3"/>
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="J44" s="21">
         <f t="shared" si="4"/>
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="K44" s="22" t="s">
         <v>60</v>
@@ -3868,28 +3873,28 @@
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="27">
+      <c r="A47" s="19">
         <v>46298.0</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="20">
         <v>300.0</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="20">
         <v>0.0</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="20">
         <v>120.0</v>
       </c>
-      <c r="E47" s="28">
+      <c r="E47" s="20">
         <v>60.0</v>
       </c>
-      <c r="F47" s="28">
+      <c r="F47" s="20">
         <v>0.0</v>
       </c>
-      <c r="G47" s="28">
+      <c r="G47" s="20">
         <v>0.0</v>
       </c>
-      <c r="H47" s="28">
+      <c r="H47" s="20">
         <v>170.0</v>
       </c>
       <c r="I47" s="21">
@@ -3900,40 +3905,64 @@
         <f t="shared" si="4"/>
         <v>790</v>
       </c>
-      <c r="K47" s="29" t="s">
+      <c r="K47" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L47" s="29" t="s">
+      <c r="L47" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="M47" s="29" t="s">
+      <c r="M47" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="30" t="s">
+      <c r="N47" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J48" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="23"/>
+      <c r="A48" s="28">
+        <v>46299.0</v>
+      </c>
+      <c r="B48" s="27">
+        <v>360.0</v>
+      </c>
+      <c r="C48" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="D48" s="27">
+        <v>100.0</v>
+      </c>
+      <c r="E48" s="27">
+        <v>90.0</v>
+      </c>
+      <c r="F48" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="G48" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="H48" s="27">
+        <v>180.0</v>
+      </c>
+      <c r="I48" s="21">
+        <f t="shared" si="3"/>
+        <v>730</v>
+      </c>
+      <c r="J48" s="21">
+        <f t="shared" si="4"/>
+        <v>710</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="30" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
+  </si>
+  <si>
+    <t>My Data, My Code — Daily Log</t>
   </si>
   <si>
     <t>Daily Activity Tracker — Instructions</t>
@@ -23,16 +26,16 @@
     <t>Save this file as &lt;YourRegistrationNumber&gt;.xlsx (e.g. 123456.xlsx). One file per student.</t>
   </si>
   <si>
-    <t>My Data, My Code — Daily Log</t>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t>Shubham Patel</t>
   </si>
   <si>
     <t>1. FILE NAME</t>
   </si>
   <si>
     <t xml:space="preserve">   Rename this file to your registration number, e.g. 123456.xlsx, before you start filling it in.</t>
-  </si>
-  <si>
-    <t>Name:</t>
   </si>
   <si>
     <t>2. WHERE TO ENTER DATA</t>
@@ -50,9 +53,6 @@
     <t>3. TIME FORMAT — ALWAYS IN MINUTES</t>
   </si>
   <si>
-    <t>Shubham Patel</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Record every duration in minutes, not hours, so totals stay easy to add and compare.</t>
   </si>
   <si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>4. COLUMN GUIDE</t>
+  </si>
+  <si>
+    <t>Registration No.:</t>
   </si>
   <si>
     <t xml:space="preserve">   Date              - the calendar date for the entry</t>
@@ -104,25 +107,22 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>Course / Section:</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
+    <t>Month:</t>
   </si>
   <si>
-    <t>Registration No.:</t>
-  </si>
-  <si>
-    <t>Course / Section:</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>Month:</t>
+    <t xml:space="preserve">   Keep every duration in minutes — do not mix hours and minutes in the same column.</t>
   </si>
   <si>
     <t>August</t>
@@ -253,6 +253,15 @@
   <si>
     <t>today i study in python</t>
   </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>today i study python</t>
+  </si>
 </sst>
 </file>
 
@@ -278,6 +287,12 @@
     <font>
       <b/>
       <sz val="13.0"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
@@ -288,26 +303,20 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -482,10 +491,10 @@
     <xf borderId="4" fillId="2" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -739,176 +748,176 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
+      <c r="A5" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
+      <c r="A6" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
+      <c r="A8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
+      <c r="A10" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>11</v>
+      <c r="A13" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>16</v>
+      <c r="A18" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>17</v>
+      <c r="A19" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>18</v>
+      <c r="A20" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>19</v>
+      <c r="A21" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
+      <c r="A22" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>21</v>
+      <c r="A23" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>22</v>
+      <c r="A24" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>23</v>
+      <c r="A25" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>24</v>
+      <c r="A26" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>25</v>
+      <c r="A27" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>26</v>
+      <c r="A28" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
+      <c r="A29" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>28</v>
+      <c r="A30" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>29</v>
+      <c r="A31" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="6"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>30</v>
+      <c r="A33" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>31</v>
+      <c r="A34" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>32</v>
+      <c r="A35" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="6"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -1898,21 +1907,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>3</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
+      <c r="A2" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="7" t="s">
-        <v>33</v>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F2" s="8">
         <v>1.2602441E7</v>
@@ -1924,16 +1933,16 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>34</v>
+      <c r="A3" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="7" t="s">
-        <v>36</v>
+      <c r="E3" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>37</v>
@@ -3747,7 +3756,7 @@
       <c r="D44" s="20">
         <v>50.0</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="20">
         <v>100.0</v>
       </c>
       <c r="F44" s="20">
@@ -3919,28 +3928,28 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="28">
+      <c r="A48" s="19">
         <v>46299.0</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="20">
         <v>360.0</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="20">
         <v>0.0</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="20">
         <v>100.0</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="20">
         <v>90.0</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="20">
         <v>0.0</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="20">
         <v>0.0</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="20">
         <v>180.0</v>
       </c>
       <c r="I48" s="21">
@@ -3951,40 +3960,64 @@
         <f t="shared" si="4"/>
         <v>710</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="K48" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L48" s="29" t="s">
+      <c r="L48" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M48" s="29" t="s">
+      <c r="M48" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="N48" s="30" t="s">
+      <c r="N48" s="23" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="23"/>
+      <c r="A49" s="27">
+        <v>46300.0</v>
+      </c>
+      <c r="B49" s="28">
+        <v>360.0</v>
+      </c>
+      <c r="C49" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="D49" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="E49" s="28">
+        <v>120.0</v>
+      </c>
+      <c r="F49" s="28">
+        <v>300.0</v>
+      </c>
+      <c r="G49" s="28">
+        <v>6.0</v>
+      </c>
+      <c r="H49" s="28">
+        <v>150.0</v>
+      </c>
+      <c r="I49" s="21">
+        <f t="shared" si="3"/>
+        <v>1050</v>
+      </c>
+      <c r="J49" s="21">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="K49" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="L49" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="N49" s="30" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="19"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A2C0A5-B9E5-4082-8F3E-72C40FB343DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3708DF-C12D-4D88-BD94-D84465FB82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   <si>
     <t>today I study networking</t>
   </si>
+  <si>
+    <t>done in mmt networking</t>
+  </si>
 </sst>
 </file>
 
@@ -536,12 +539,12 @@
     <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1938,7 +1941,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="22"/>
@@ -1959,18 +1962,18 @@
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="24">
         <v>12602441</v>
       </c>
-      <c r="G2" s="25"/>
+      <c r="G2" s="26"/>
       <c r="M2" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""Fill an appropriate value for this cell based on the table context"")"),"=AI(""Fill an appropriate value for this cell based on the table context"")")</f>
         <v>=AI("Fill an appropriate value for this cell based on the table context")</v>
@@ -1980,21 +1983,21 @@
       <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="25"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="22"/>
@@ -4353,26 +4356,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="18"/>
+      <c r="A56" s="14">
+        <v>46307</v>
+      </c>
+      <c r="B56" s="15">
+        <v>240</v>
+      </c>
+      <c r="C56" s="15">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15">
+        <v>360</v>
+      </c>
+      <c r="E56" s="15">
+        <v>0</v>
+      </c>
+      <c r="F56" s="15">
+        <v>0</v>
+      </c>
+      <c r="G56" s="15">
+        <v>0</v>
+      </c>
+      <c r="H56" s="15">
+        <v>200</v>
+      </c>
+      <c r="I56" s="16">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="J56" s="16">
+        <f t="shared" si="3"/>
+        <v>640</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L56" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N56" s="18" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3708DF-C12D-4D88-BD94-D84465FB82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A24FE9-F298-4699-868E-2FB5A2EC0538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>done in mmt networking</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>done MTT c++</t>
   </si>
 </sst>
 </file>
@@ -4402,26 +4408,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J57" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="18"/>
+      <c r="A57" s="14">
+        <v>46308</v>
+      </c>
+      <c r="B57" s="15">
+        <v>300</v>
+      </c>
+      <c r="C57" s="15">
+        <v>0</v>
+      </c>
+      <c r="D57" s="15">
+        <v>300</v>
+      </c>
+      <c r="E57" s="15">
+        <v>0</v>
+      </c>
+      <c r="F57" s="15">
+        <v>0</v>
+      </c>
+      <c r="G57" s="15">
+        <v>0</v>
+      </c>
+      <c r="H57" s="15">
+        <v>200</v>
+      </c>
+      <c r="I57" s="16">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="J57" s="16">
+        <f t="shared" si="3"/>
+        <v>640</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L57" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M57" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="18" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A24FE9-F298-4699-868E-2FB5A2EC0538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6517D4A-7102-4F2F-83E8-DCF78128F5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +305,12 @@
   </si>
   <si>
     <t>done MTT c++</t>
+  </si>
+  <si>
+    <t>prepare for exam</t>
+  </si>
+  <si>
+    <t>anylitical skill prepration</t>
   </si>
 </sst>
 </file>
@@ -4454,48 +4458,96 @@
       </c>
     </row>
     <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J58" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="18"/>
+      <c r="A58" s="14">
+        <v>46309</v>
+      </c>
+      <c r="B58" s="15">
+        <v>360</v>
+      </c>
+      <c r="C58" s="15">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15">
+        <v>300</v>
+      </c>
+      <c r="E58" s="15">
+        <v>0</v>
+      </c>
+      <c r="F58" s="15">
+        <v>0</v>
+      </c>
+      <c r="G58" s="15">
+        <v>0</v>
+      </c>
+      <c r="H58" s="15">
+        <v>200</v>
+      </c>
+      <c r="I58" s="16">
+        <f t="shared" si="2"/>
+        <v>860</v>
+      </c>
+      <c r="J58" s="16">
+        <f t="shared" si="3"/>
+        <v>580</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M58" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N58" s="18" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J59" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="18"/>
+      <c r="A59" s="14">
+        <v>46310</v>
+      </c>
+      <c r="B59" s="15">
+        <v>300</v>
+      </c>
+      <c r="C59" s="15">
+        <v>0</v>
+      </c>
+      <c r="D59" s="15">
+        <v>320</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0</v>
+      </c>
+      <c r="F59" s="15">
+        <v>0</v>
+      </c>
+      <c r="G59" s="15">
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <v>150</v>
+      </c>
+      <c r="I59" s="16">
+        <f t="shared" si="2"/>
+        <v>770</v>
+      </c>
+      <c r="J59" s="16">
+        <f t="shared" si="3"/>
+        <v>670</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L59" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N59" s="18" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6517D4A-7102-4F2F-83E8-DCF78128F5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B8B2E-CD9B-4777-8B93-46645DFB3910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>anylitical skill prepration</t>
+  </si>
+  <si>
+    <t>today I study english</t>
   </si>
 </sst>
 </file>
@@ -2094,11 +2097,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="11">
-        <f t="shared" ref="I6:I18" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I19" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="11">
-        <f t="shared" ref="J6:J18" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J19" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="12" t="s">
@@ -2691,10 +2694,13 @@
       <c r="H19" s="15">
         <v>140</v>
       </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="16" t="e">
-        <f>IF(#REF!="","",1440-#REF!)</f>
-        <v>#REF!</v>
+      <c r="I19" s="16">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J19" s="16">
+        <f t="shared" si="1"/>
+        <v>380</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>53</v>
@@ -2785,7 +2791,7 @@
         <v>1065</v>
       </c>
       <c r="J21" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J21" si="4">IF(I21="","",1440-I21)</f>
         <v>375</v>
       </c>
       <c r="K21" s="17" t="s">
@@ -4550,26 +4556,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J60" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="18"/>
+      <c r="A60" s="14">
+        <v>46311</v>
+      </c>
+      <c r="B60" s="15">
+        <v>300</v>
+      </c>
+      <c r="C60" s="15">
+        <v>0</v>
+      </c>
+      <c r="D60" s="15">
+        <v>200</v>
+      </c>
+      <c r="E60" s="15">
+        <v>0</v>
+      </c>
+      <c r="F60" s="15">
+        <v>0</v>
+      </c>
+      <c r="G60" s="15">
+        <v>0</v>
+      </c>
+      <c r="H60" s="15">
+        <v>200</v>
+      </c>
+      <c r="I60" s="16">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+      <c r="J60" s="16">
+        <f t="shared" si="3"/>
+        <v>740</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N60" s="18" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
@@ -9289,11 +9319,11 @@
       <c r="G275" s="15"/>
       <c r="H275" s="15"/>
       <c r="I275" s="16" t="str">
-        <f t="shared" ref="I275:I401" si="4">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
+        <f t="shared" ref="I275:I401" si="5">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
         <v/>
       </c>
       <c r="J275" s="16" t="str">
-        <f t="shared" ref="J275:J401" si="5">IF(I275="","",1440-I275)</f>
+        <f t="shared" ref="J275:J401" si="6">IF(I275="","",1440-I275)</f>
         <v/>
       </c>
       <c r="K275" s="17"/>
@@ -9311,11 +9341,11 @@
       <c r="G276" s="15"/>
       <c r="H276" s="15"/>
       <c r="I276" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J276" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K276" s="17"/>
@@ -9333,11 +9363,11 @@
       <c r="G277" s="15"/>
       <c r="H277" s="15"/>
       <c r="I277" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J277" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K277" s="17"/>
@@ -9355,11 +9385,11 @@
       <c r="G278" s="15"/>
       <c r="H278" s="15"/>
       <c r="I278" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J278" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K278" s="17"/>
@@ -9377,11 +9407,11 @@
       <c r="G279" s="15"/>
       <c r="H279" s="15"/>
       <c r="I279" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J279" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K279" s="17"/>
@@ -9399,11 +9429,11 @@
       <c r="G280" s="15"/>
       <c r="H280" s="15"/>
       <c r="I280" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J280" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K280" s="17"/>
@@ -9421,11 +9451,11 @@
       <c r="G281" s="15"/>
       <c r="H281" s="15"/>
       <c r="I281" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J281" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K281" s="17"/>
@@ -9443,11 +9473,11 @@
       <c r="G282" s="15"/>
       <c r="H282" s="15"/>
       <c r="I282" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J282" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K282" s="17"/>
@@ -9465,11 +9495,11 @@
       <c r="G283" s="15"/>
       <c r="H283" s="15"/>
       <c r="I283" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J283" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K283" s="17"/>
@@ -9487,11 +9517,11 @@
       <c r="G284" s="15"/>
       <c r="H284" s="15"/>
       <c r="I284" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J284" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K284" s="17"/>
@@ -9509,11 +9539,11 @@
       <c r="G285" s="15"/>
       <c r="H285" s="15"/>
       <c r="I285" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J285" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K285" s="17"/>
@@ -9531,11 +9561,11 @@
       <c r="G286" s="15"/>
       <c r="H286" s="15"/>
       <c r="I286" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J286" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K286" s="17"/>
@@ -9553,11 +9583,11 @@
       <c r="G287" s="15"/>
       <c r="H287" s="15"/>
       <c r="I287" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J287" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K287" s="17"/>
@@ -9575,11 +9605,11 @@
       <c r="G288" s="15"/>
       <c r="H288" s="15"/>
       <c r="I288" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J288" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K288" s="17"/>
@@ -9597,11 +9627,11 @@
       <c r="G289" s="15"/>
       <c r="H289" s="15"/>
       <c r="I289" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J289" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K289" s="17"/>
@@ -9619,11 +9649,11 @@
       <c r="G290" s="15"/>
       <c r="H290" s="15"/>
       <c r="I290" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J290" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K290" s="17"/>
@@ -9641,11 +9671,11 @@
       <c r="G291" s="15"/>
       <c r="H291" s="15"/>
       <c r="I291" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J291" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K291" s="17"/>
@@ -9663,11 +9693,11 @@
       <c r="G292" s="15"/>
       <c r="H292" s="15"/>
       <c r="I292" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J292" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K292" s="17"/>
@@ -9685,11 +9715,11 @@
       <c r="G293" s="15"/>
       <c r="H293" s="15"/>
       <c r="I293" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J293" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K293" s="17"/>
@@ -9707,11 +9737,11 @@
       <c r="G294" s="15"/>
       <c r="H294" s="15"/>
       <c r="I294" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J294" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K294" s="17"/>
@@ -9729,11 +9759,11 @@
       <c r="G295" s="15"/>
       <c r="H295" s="15"/>
       <c r="I295" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J295" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K295" s="17"/>
@@ -9751,11 +9781,11 @@
       <c r="G296" s="15"/>
       <c r="H296" s="15"/>
       <c r="I296" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J296" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K296" s="17"/>
@@ -9773,11 +9803,11 @@
       <c r="G297" s="15"/>
       <c r="H297" s="15"/>
       <c r="I297" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J297" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K297" s="17"/>
@@ -9795,11 +9825,11 @@
       <c r="G298" s="15"/>
       <c r="H298" s="15"/>
       <c r="I298" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J298" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K298" s="17"/>
@@ -9817,11 +9847,11 @@
       <c r="G299" s="15"/>
       <c r="H299" s="15"/>
       <c r="I299" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J299" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K299" s="17"/>
@@ -9839,11 +9869,11 @@
       <c r="G300" s="15"/>
       <c r="H300" s="15"/>
       <c r="I300" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J300" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K300" s="17"/>
@@ -9861,11 +9891,11 @@
       <c r="G301" s="15"/>
       <c r="H301" s="15"/>
       <c r="I301" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J301" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K301" s="17"/>
@@ -9883,11 +9913,11 @@
       <c r="G302" s="15"/>
       <c r="H302" s="15"/>
       <c r="I302" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J302" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K302" s="17"/>
@@ -9905,11 +9935,11 @@
       <c r="G303" s="15"/>
       <c r="H303" s="15"/>
       <c r="I303" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J303" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K303" s="17"/>
@@ -9927,11 +9957,11 @@
       <c r="G304" s="15"/>
       <c r="H304" s="15"/>
       <c r="I304" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J304" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K304" s="17"/>
@@ -9949,11 +9979,11 @@
       <c r="G305" s="15"/>
       <c r="H305" s="15"/>
       <c r="I305" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J305" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K305" s="17"/>
@@ -9971,11 +10001,11 @@
       <c r="G306" s="15"/>
       <c r="H306" s="15"/>
       <c r="I306" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J306" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K306" s="17"/>
@@ -9993,11 +10023,11 @@
       <c r="G307" s="15"/>
       <c r="H307" s="15"/>
       <c r="I307" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J307" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K307" s="17"/>
@@ -10015,11 +10045,11 @@
       <c r="G308" s="15"/>
       <c r="H308" s="15"/>
       <c r="I308" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J308" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K308" s="17"/>
@@ -10037,11 +10067,11 @@
       <c r="G309" s="15"/>
       <c r="H309" s="15"/>
       <c r="I309" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J309" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K309" s="17"/>
@@ -10059,11 +10089,11 @@
       <c r="G310" s="15"/>
       <c r="H310" s="15"/>
       <c r="I310" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J310" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K310" s="17"/>
@@ -10081,11 +10111,11 @@
       <c r="G311" s="15"/>
       <c r="H311" s="15"/>
       <c r="I311" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J311" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K311" s="17"/>
@@ -10103,11 +10133,11 @@
       <c r="G312" s="15"/>
       <c r="H312" s="15"/>
       <c r="I312" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J312" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K312" s="17"/>
@@ -10125,11 +10155,11 @@
       <c r="G313" s="15"/>
       <c r="H313" s="15"/>
       <c r="I313" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J313" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K313" s="17"/>
@@ -10147,11 +10177,11 @@
       <c r="G314" s="15"/>
       <c r="H314" s="15"/>
       <c r="I314" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J314" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K314" s="17"/>
@@ -10169,11 +10199,11 @@
       <c r="G315" s="15"/>
       <c r="H315" s="15"/>
       <c r="I315" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J315" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K315" s="17"/>
@@ -10191,11 +10221,11 @@
       <c r="G316" s="15"/>
       <c r="H316" s="15"/>
       <c r="I316" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J316" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K316" s="17"/>
@@ -10213,11 +10243,11 @@
       <c r="G317" s="15"/>
       <c r="H317" s="15"/>
       <c r="I317" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J317" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K317" s="17"/>
@@ -10235,11 +10265,11 @@
       <c r="G318" s="15"/>
       <c r="H318" s="15"/>
       <c r="I318" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J318" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K318" s="17"/>
@@ -10257,11 +10287,11 @@
       <c r="G319" s="15"/>
       <c r="H319" s="15"/>
       <c r="I319" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J319" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K319" s="17"/>
@@ -10279,11 +10309,11 @@
       <c r="G320" s="15"/>
       <c r="H320" s="15"/>
       <c r="I320" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J320" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K320" s="17"/>
@@ -10301,11 +10331,11 @@
       <c r="G321" s="15"/>
       <c r="H321" s="15"/>
       <c r="I321" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J321" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K321" s="17"/>
@@ -10323,11 +10353,11 @@
       <c r="G322" s="15"/>
       <c r="H322" s="15"/>
       <c r="I322" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J322" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K322" s="17"/>
@@ -10345,11 +10375,11 @@
       <c r="G323" s="15"/>
       <c r="H323" s="15"/>
       <c r="I323" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J323" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K323" s="17"/>
@@ -10367,11 +10397,11 @@
       <c r="G324" s="15"/>
       <c r="H324" s="15"/>
       <c r="I324" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J324" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K324" s="17"/>
@@ -10389,11 +10419,11 @@
       <c r="G325" s="15"/>
       <c r="H325" s="15"/>
       <c r="I325" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J325" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K325" s="17"/>
@@ -10411,11 +10441,11 @@
       <c r="G326" s="15"/>
       <c r="H326" s="15"/>
       <c r="I326" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J326" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K326" s="17"/>
@@ -10433,11 +10463,11 @@
       <c r="G327" s="15"/>
       <c r="H327" s="15"/>
       <c r="I327" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J327" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K327" s="17"/>
@@ -10455,11 +10485,11 @@
       <c r="G328" s="15"/>
       <c r="H328" s="15"/>
       <c r="I328" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J328" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K328" s="17"/>
@@ -10477,11 +10507,11 @@
       <c r="G329" s="15"/>
       <c r="H329" s="15"/>
       <c r="I329" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J329" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K329" s="17"/>
@@ -10499,11 +10529,11 @@
       <c r="G330" s="15"/>
       <c r="H330" s="15"/>
       <c r="I330" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J330" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K330" s="17"/>
@@ -10521,11 +10551,11 @@
       <c r="G331" s="15"/>
       <c r="H331" s="15"/>
       <c r="I331" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J331" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K331" s="17"/>
@@ -10543,11 +10573,11 @@
       <c r="G332" s="15"/>
       <c r="H332" s="15"/>
       <c r="I332" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J332" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K332" s="17"/>
@@ -10565,11 +10595,11 @@
       <c r="G333" s="15"/>
       <c r="H333" s="15"/>
       <c r="I333" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J333" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K333" s="17"/>
@@ -10587,11 +10617,11 @@
       <c r="G334" s="15"/>
       <c r="H334" s="15"/>
       <c r="I334" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J334" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K334" s="17"/>
@@ -10609,11 +10639,11 @@
       <c r="G335" s="15"/>
       <c r="H335" s="15"/>
       <c r="I335" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J335" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K335" s="17"/>
@@ -10631,11 +10661,11 @@
       <c r="G336" s="15"/>
       <c r="H336" s="15"/>
       <c r="I336" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J336" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K336" s="17"/>
@@ -10653,11 +10683,11 @@
       <c r="G337" s="15"/>
       <c r="H337" s="15"/>
       <c r="I337" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J337" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K337" s="17"/>
@@ -10675,11 +10705,11 @@
       <c r="G338" s="15"/>
       <c r="H338" s="15"/>
       <c r="I338" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J338" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K338" s="17"/>
@@ -10697,11 +10727,11 @@
       <c r="G339" s="15"/>
       <c r="H339" s="15"/>
       <c r="I339" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J339" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K339" s="17"/>
@@ -10719,11 +10749,11 @@
       <c r="G340" s="15"/>
       <c r="H340" s="15"/>
       <c r="I340" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J340" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K340" s="17"/>
@@ -10741,11 +10771,11 @@
       <c r="G341" s="15"/>
       <c r="H341" s="15"/>
       <c r="I341" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J341" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K341" s="17"/>
@@ -10763,11 +10793,11 @@
       <c r="G342" s="15"/>
       <c r="H342" s="15"/>
       <c r="I342" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J342" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K342" s="17"/>
@@ -10785,11 +10815,11 @@
       <c r="G343" s="15"/>
       <c r="H343" s="15"/>
       <c r="I343" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J343" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K343" s="17"/>
@@ -10807,11 +10837,11 @@
       <c r="G344" s="15"/>
       <c r="H344" s="15"/>
       <c r="I344" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J344" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K344" s="17"/>
@@ -10829,11 +10859,11 @@
       <c r="G345" s="15"/>
       <c r="H345" s="15"/>
       <c r="I345" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J345" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K345" s="17"/>
@@ -10851,11 +10881,11 @@
       <c r="G346" s="15"/>
       <c r="H346" s="15"/>
       <c r="I346" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J346" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K346" s="17"/>
@@ -10873,11 +10903,11 @@
       <c r="G347" s="15"/>
       <c r="H347" s="15"/>
       <c r="I347" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J347" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K347" s="17"/>
@@ -10895,11 +10925,11 @@
       <c r="G348" s="15"/>
       <c r="H348" s="15"/>
       <c r="I348" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J348" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K348" s="17"/>
@@ -10917,11 +10947,11 @@
       <c r="G349" s="15"/>
       <c r="H349" s="15"/>
       <c r="I349" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J349" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K349" s="17"/>
@@ -10939,11 +10969,11 @@
       <c r="G350" s="15"/>
       <c r="H350" s="15"/>
       <c r="I350" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J350" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K350" s="17"/>
@@ -10961,11 +10991,11 @@
       <c r="G351" s="15"/>
       <c r="H351" s="15"/>
       <c r="I351" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J351" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K351" s="17"/>
@@ -10983,11 +11013,11 @@
       <c r="G352" s="15"/>
       <c r="H352" s="15"/>
       <c r="I352" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J352" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K352" s="17"/>
@@ -11005,11 +11035,11 @@
       <c r="G353" s="15"/>
       <c r="H353" s="15"/>
       <c r="I353" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J353" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K353" s="17"/>
@@ -11027,11 +11057,11 @@
       <c r="G354" s="15"/>
       <c r="H354" s="15"/>
       <c r="I354" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J354" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K354" s="17"/>
@@ -11049,11 +11079,11 @@
       <c r="G355" s="15"/>
       <c r="H355" s="15"/>
       <c r="I355" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J355" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K355" s="17"/>
@@ -11071,11 +11101,11 @@
       <c r="G356" s="15"/>
       <c r="H356" s="15"/>
       <c r="I356" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J356" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K356" s="17"/>
@@ -11093,11 +11123,11 @@
       <c r="G357" s="15"/>
       <c r="H357" s="15"/>
       <c r="I357" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J357" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K357" s="17"/>
@@ -11115,11 +11145,11 @@
       <c r="G358" s="15"/>
       <c r="H358" s="15"/>
       <c r="I358" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J358" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K358" s="17"/>
@@ -11137,11 +11167,11 @@
       <c r="G359" s="15"/>
       <c r="H359" s="15"/>
       <c r="I359" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J359" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K359" s="17"/>
@@ -11159,11 +11189,11 @@
       <c r="G360" s="15"/>
       <c r="H360" s="15"/>
       <c r="I360" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J360" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K360" s="17"/>
@@ -11181,11 +11211,11 @@
       <c r="G361" s="15"/>
       <c r="H361" s="15"/>
       <c r="I361" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J361" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K361" s="17"/>
@@ -11203,11 +11233,11 @@
       <c r="G362" s="15"/>
       <c r="H362" s="15"/>
       <c r="I362" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J362" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K362" s="17"/>
@@ -11225,11 +11255,11 @@
       <c r="G363" s="15"/>
       <c r="H363" s="15"/>
       <c r="I363" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J363" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K363" s="17"/>
@@ -11247,11 +11277,11 @@
       <c r="G364" s="15"/>
       <c r="H364" s="15"/>
       <c r="I364" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J364" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K364" s="17"/>
@@ -11269,11 +11299,11 @@
       <c r="G365" s="15"/>
       <c r="H365" s="15"/>
       <c r="I365" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J365" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K365" s="17"/>
@@ -11291,11 +11321,11 @@
       <c r="G366" s="15"/>
       <c r="H366" s="15"/>
       <c r="I366" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J366" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K366" s="17"/>
@@ -11313,11 +11343,11 @@
       <c r="G367" s="15"/>
       <c r="H367" s="15"/>
       <c r="I367" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J367" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K367" s="17"/>
@@ -11335,11 +11365,11 @@
       <c r="G368" s="15"/>
       <c r="H368" s="15"/>
       <c r="I368" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J368" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K368" s="17"/>
@@ -11357,11 +11387,11 @@
       <c r="G369" s="15"/>
       <c r="H369" s="15"/>
       <c r="I369" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J369" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K369" s="17"/>
@@ -11379,11 +11409,11 @@
       <c r="G370" s="15"/>
       <c r="H370" s="15"/>
       <c r="I370" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J370" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K370" s="17"/>
@@ -11401,11 +11431,11 @@
       <c r="G371" s="15"/>
       <c r="H371" s="15"/>
       <c r="I371" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J371" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K371" s="17"/>
@@ -11423,11 +11453,11 @@
       <c r="G372" s="15"/>
       <c r="H372" s="15"/>
       <c r="I372" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J372" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K372" s="17"/>
@@ -11445,11 +11475,11 @@
       <c r="G373" s="15"/>
       <c r="H373" s="15"/>
       <c r="I373" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J373" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K373" s="17"/>
@@ -11467,11 +11497,11 @@
       <c r="G374" s="15"/>
       <c r="H374" s="15"/>
       <c r="I374" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J374" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K374" s="17"/>
@@ -11489,11 +11519,11 @@
       <c r="G375" s="15"/>
       <c r="H375" s="15"/>
       <c r="I375" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J375" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K375" s="17"/>
@@ -11511,11 +11541,11 @@
       <c r="G376" s="15"/>
       <c r="H376" s="15"/>
       <c r="I376" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J376" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K376" s="17"/>
@@ -11533,11 +11563,11 @@
       <c r="G377" s="15"/>
       <c r="H377" s="15"/>
       <c r="I377" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J377" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K377" s="17"/>
@@ -11555,11 +11585,11 @@
       <c r="G378" s="15"/>
       <c r="H378" s="15"/>
       <c r="I378" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J378" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K378" s="17"/>
@@ -11577,11 +11607,11 @@
       <c r="G379" s="15"/>
       <c r="H379" s="15"/>
       <c r="I379" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J379" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K379" s="17"/>
@@ -11599,11 +11629,11 @@
       <c r="G380" s="15"/>
       <c r="H380" s="15"/>
       <c r="I380" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J380" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K380" s="17"/>
@@ -11621,11 +11651,11 @@
       <c r="G381" s="15"/>
       <c r="H381" s="15"/>
       <c r="I381" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J381" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K381" s="17"/>
@@ -11643,11 +11673,11 @@
       <c r="G382" s="15"/>
       <c r="H382" s="15"/>
       <c r="I382" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J382" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K382" s="17"/>
@@ -11665,11 +11695,11 @@
       <c r="G383" s="15"/>
       <c r="H383" s="15"/>
       <c r="I383" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J383" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K383" s="17"/>
@@ -11687,11 +11717,11 @@
       <c r="G384" s="15"/>
       <c r="H384" s="15"/>
       <c r="I384" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J384" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K384" s="17"/>
@@ -11709,11 +11739,11 @@
       <c r="G385" s="15"/>
       <c r="H385" s="15"/>
       <c r="I385" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J385" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K385" s="17"/>
@@ -11731,11 +11761,11 @@
       <c r="G386" s="15"/>
       <c r="H386" s="15"/>
       <c r="I386" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J386" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K386" s="17"/>
@@ -11753,11 +11783,11 @@
       <c r="G387" s="15"/>
       <c r="H387" s="15"/>
       <c r="I387" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J387" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K387" s="17"/>
@@ -11775,11 +11805,11 @@
       <c r="G388" s="15"/>
       <c r="H388" s="15"/>
       <c r="I388" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J388" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K388" s="17"/>
@@ -11797,11 +11827,11 @@
       <c r="G389" s="15"/>
       <c r="H389" s="15"/>
       <c r="I389" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J389" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K389" s="17"/>
@@ -11819,11 +11849,11 @@
       <c r="G390" s="15"/>
       <c r="H390" s="15"/>
       <c r="I390" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J390" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K390" s="17"/>
@@ -11841,11 +11871,11 @@
       <c r="G391" s="15"/>
       <c r="H391" s="15"/>
       <c r="I391" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J391" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K391" s="17"/>
@@ -11863,11 +11893,11 @@
       <c r="G392" s="15"/>
       <c r="H392" s="15"/>
       <c r="I392" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J392" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K392" s="17"/>
@@ -11885,11 +11915,11 @@
       <c r="G393" s="15"/>
       <c r="H393" s="15"/>
       <c r="I393" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J393" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K393" s="17"/>
@@ -11907,11 +11937,11 @@
       <c r="G394" s="15"/>
       <c r="H394" s="15"/>
       <c r="I394" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J394" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K394" s="17"/>
@@ -11929,11 +11959,11 @@
       <c r="G395" s="15"/>
       <c r="H395" s="15"/>
       <c r="I395" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J395" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K395" s="17"/>
@@ -11951,11 +11981,11 @@
       <c r="G396" s="15"/>
       <c r="H396" s="15"/>
       <c r="I396" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J396" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K396" s="17"/>
@@ -11973,11 +12003,11 @@
       <c r="G397" s="15"/>
       <c r="H397" s="15"/>
       <c r="I397" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J397" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K397" s="17"/>
@@ -11995,11 +12025,11 @@
       <c r="G398" s="15"/>
       <c r="H398" s="15"/>
       <c r="I398" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J398" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K398" s="17"/>
@@ -12017,11 +12047,11 @@
       <c r="G399" s="15"/>
       <c r="H399" s="15"/>
       <c r="I399" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J399" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K399" s="17"/>
@@ -12039,11 +12069,11 @@
       <c r="G400" s="15"/>
       <c r="H400" s="15"/>
       <c r="I400" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J400" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K400" s="17"/>
@@ -12061,11 +12091,11 @@
       <c r="G401" s="15"/>
       <c r="H401" s="15"/>
       <c r="I401" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J401" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K401" s="17"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B8B2E-CD9B-4777-8B93-46645DFB3910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB76A86-534C-4190-95FB-0B2D894DC7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>today I study english</t>
+  </si>
+  <si>
+    <t>today I finished exam</t>
   </si>
 </sst>
 </file>
@@ -4602,26 +4605,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J61" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="18"/>
+      <c r="A61" s="14">
+        <v>46312</v>
+      </c>
+      <c r="B61" s="15">
+        <v>360</v>
+      </c>
+      <c r="C61" s="15">
+        <v>0</v>
+      </c>
+      <c r="D61" s="15">
+        <v>120</v>
+      </c>
+      <c r="E61" s="15">
+        <v>60</v>
+      </c>
+      <c r="F61" s="15">
+        <v>0</v>
+      </c>
+      <c r="G61" s="15">
+        <v>0</v>
+      </c>
+      <c r="H61" s="15">
+        <v>200</v>
+      </c>
+      <c r="I61" s="16">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J61" s="16">
+        <f t="shared" si="3"/>
+        <v>700</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L61" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M61" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N61" s="18" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB76A86-534C-4190-95FB-0B2D894DC7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE40600A-387B-48E0-A9D8-13C4BAF4F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>today I finished exam</t>
+  </si>
+  <si>
+    <t>today I study c++</t>
   </si>
 </sst>
 </file>
@@ -4651,26 +4654,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="14"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J62" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="18"/>
+      <c r="A62" s="14">
+        <v>46313</v>
+      </c>
+      <c r="B62" s="15">
+        <v>300</v>
+      </c>
+      <c r="C62" s="15">
+        <v>0</v>
+      </c>
+      <c r="D62" s="15">
+        <v>60</v>
+      </c>
+      <c r="E62" s="15">
+        <v>60</v>
+      </c>
+      <c r="F62" s="15">
+        <v>0</v>
+      </c>
+      <c r="G62" s="15">
+        <v>0</v>
+      </c>
+      <c r="H62" s="15">
+        <v>200</v>
+      </c>
+      <c r="I62" s="16">
+        <f t="shared" si="2"/>
+        <v>620</v>
+      </c>
+      <c r="J62" s="16">
+        <f t="shared" si="3"/>
+        <v>820</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L62" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M62" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N62" s="18" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE40600A-387B-48E0-A9D8-13C4BAF4F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F8867C-D106-4938-9585-D57C1517B1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>today I study c++</t>
+  </si>
+  <si>
+    <t>today I start DSA</t>
   </si>
 </sst>
 </file>
@@ -4700,26 +4703,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="18"/>
+      <c r="A63" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B63" s="15">
+        <v>360</v>
+      </c>
+      <c r="C63" s="15">
+        <v>0</v>
+      </c>
+      <c r="D63" s="15">
+        <v>120</v>
+      </c>
+      <c r="E63" s="15">
+        <v>100</v>
+      </c>
+      <c r="F63" s="15">
+        <v>50</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1</v>
+      </c>
+      <c r="H63" s="15">
+        <v>200</v>
+      </c>
+      <c r="I63" s="16">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J63" s="16">
+        <f t="shared" si="3"/>
+        <v>610</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="18" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F8867C-D106-4938-9585-D57C1517B1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03575C3E-09D5-4E6B-B1C5-071C333F6074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4749,26 +4749,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="14"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="18"/>
+      <c r="A64" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B64" s="15">
+        <v>300</v>
+      </c>
+      <c r="C64" s="15">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15">
+        <v>120</v>
+      </c>
+      <c r="E64" s="15">
+        <v>100</v>
+      </c>
+      <c r="F64" s="15">
+        <v>0</v>
+      </c>
+      <c r="G64" s="15">
+        <v>0</v>
+      </c>
+      <c r="H64" s="15">
+        <v>210</v>
+      </c>
+      <c r="I64" s="16">
+        <f t="shared" si="2"/>
+        <v>730</v>
+      </c>
+      <c r="J64" s="16">
+        <f t="shared" si="3"/>
+        <v>710</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L64" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M64" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N64" s="18" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03575C3E-09D5-4E6B-B1C5-071C333F6074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18263DE1-AAC6-474D-9647-E4B978B11221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>today I start DSA</t>
+  </si>
+  <si>
+    <t>today I study time complexity</t>
   </si>
 </sst>
 </file>
@@ -4795,26 +4798,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="14"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="18"/>
+      <c r="A65" s="14">
+        <v>46316</v>
+      </c>
+      <c r="B65" s="15">
+        <v>300</v>
+      </c>
+      <c r="C65" s="15">
+        <v>0</v>
+      </c>
+      <c r="D65" s="15">
+        <v>120</v>
+      </c>
+      <c r="E65" s="15">
+        <v>120</v>
+      </c>
+      <c r="F65" s="15">
+        <v>300</v>
+      </c>
+      <c r="G65" s="15">
+        <v>6</v>
+      </c>
+      <c r="H65" s="15">
+        <v>180</v>
+      </c>
+      <c r="I65" s="16">
+        <f t="shared" si="2"/>
+        <v>1020</v>
+      </c>
+      <c r="J65" s="16">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L65" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M65" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N65" s="18" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18263DE1-AAC6-474D-9647-E4B978B11221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0342B4BB-A37E-47E1-BF52-EC06CC3F18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>today I study time complexity</t>
+  </si>
+  <si>
+    <t>today I study pattern question</t>
   </si>
 </sst>
 </file>
@@ -4844,26 +4847,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="14"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="18"/>
+      <c r="A66" s="14">
+        <v>46317</v>
+      </c>
+      <c r="B66" s="15">
+        <v>300</v>
+      </c>
+      <c r="C66" s="15">
+        <v>0</v>
+      </c>
+      <c r="D66" s="15">
+        <v>120</v>
+      </c>
+      <c r="E66" s="15">
+        <v>100</v>
+      </c>
+      <c r="F66" s="15">
+        <v>150</v>
+      </c>
+      <c r="G66" s="15">
+        <v>3</v>
+      </c>
+      <c r="H66" s="15">
+        <v>200</v>
+      </c>
+      <c r="I66" s="16">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J66" s="16">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M66" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N66" s="18" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0342B4BB-A37E-47E1-BF52-EC06CC3F18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC085EA3-E55F-473B-A996-8D4C62A94DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>today I study pattern question</t>
+  </si>
+  <si>
+    <t>today I study python</t>
   </si>
 </sst>
 </file>
@@ -4893,26 +4896,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="14"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J67" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="18"/>
+      <c r="A67" s="14">
+        <v>46318</v>
+      </c>
+      <c r="B67" s="15">
+        <v>300</v>
+      </c>
+      <c r="C67" s="15">
+        <v>0</v>
+      </c>
+      <c r="D67" s="15">
+        <v>100</v>
+      </c>
+      <c r="E67" s="15">
+        <v>60</v>
+      </c>
+      <c r="F67" s="15">
+        <v>200</v>
+      </c>
+      <c r="G67" s="15">
+        <v>5</v>
+      </c>
+      <c r="H67" s="15">
+        <v>200</v>
+      </c>
+      <c r="I67" s="16">
+        <f t="shared" si="2"/>
+        <v>860</v>
+      </c>
+      <c r="J67" s="16">
+        <f t="shared" si="3"/>
+        <v>580</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L67" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N67" s="18" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC085EA3-E55F-473B-A996-8D4C62A94DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A469E1E1-C627-4DF6-810A-561F516DEBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4942,26 +4942,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="18"/>
+      <c r="A68" s="14">
+        <v>46319</v>
+      </c>
+      <c r="B68" s="15">
+        <v>300</v>
+      </c>
+      <c r="C68" s="15">
+        <v>0</v>
+      </c>
+      <c r="D68" s="15">
+        <v>100</v>
+      </c>
+      <c r="E68" s="15">
+        <v>120</v>
+      </c>
+      <c r="F68" s="15">
+        <v>50</v>
+      </c>
+      <c r="G68" s="15">
+        <v>2</v>
+      </c>
+      <c r="H68" s="15">
+        <v>180</v>
+      </c>
+      <c r="I68" s="16">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="J68" s="16">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L68" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N68" s="18" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="69" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A469E1E1-C627-4DF6-810A-561F516DEBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D870B20A-511E-4451-B8B3-0B86377B58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>today I study python</t>
+  </si>
+  <si>
+    <t>assignment c++</t>
   </si>
 </sst>
 </file>
@@ -4958,7 +4961,7 @@
         <v>120</v>
       </c>
       <c r="F68" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G68" s="15">
         <v>2</v>
@@ -4968,11 +4971,11 @@
       </c>
       <c r="I68" s="16">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="J68" s="16">
         <f t="shared" si="3"/>
-        <v>690</v>
+        <v>640</v>
       </c>
       <c r="K68" s="17" t="s">
         <v>80</v>
@@ -4988,26 +4991,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="14"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
-      <c r="M69" s="17"/>
-      <c r="N69" s="18"/>
+      <c r="A69" s="14">
+        <v>46320</v>
+      </c>
+      <c r="B69" s="15">
+        <v>300</v>
+      </c>
+      <c r="C69" s="15">
+        <v>10</v>
+      </c>
+      <c r="D69" s="15">
+        <v>120</v>
+      </c>
+      <c r="E69" s="15">
+        <v>200</v>
+      </c>
+      <c r="F69" s="15">
+        <v>0</v>
+      </c>
+      <c r="G69" s="15">
+        <v>0</v>
+      </c>
+      <c r="H69" s="15">
+        <v>200</v>
+      </c>
+      <c r="I69" s="16">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J69" s="16">
+        <f t="shared" si="3"/>
+        <v>610</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L69" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M69" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="18" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="70" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D870B20A-511E-4451-B8B3-0B86377B58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF80970B-9A2F-4FEE-9448-A8647099A502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5037,26 +5037,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="14"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="18"/>
+      <c r="A70" s="14">
+        <v>46321</v>
+      </c>
+      <c r="B70" s="15">
+        <v>300</v>
+      </c>
+      <c r="C70" s="15">
+        <v>0</v>
+      </c>
+      <c r="D70" s="15">
+        <v>120</v>
+      </c>
+      <c r="E70" s="15">
+        <v>180</v>
+      </c>
+      <c r="F70" s="15">
+        <v>0</v>
+      </c>
+      <c r="G70" s="15">
+        <v>0</v>
+      </c>
+      <c r="H70" s="15">
+        <v>180</v>
+      </c>
+      <c r="I70" s="16">
+        <f t="shared" si="2"/>
+        <v>780</v>
+      </c>
+      <c r="J70" s="16">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M70" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="18" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="71" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF80970B-9A2F-4FEE-9448-A8647099A502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9751A9E-942E-4741-9AD3-ECCD3F27CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5083,26 +5083,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="14"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="18"/>
+      <c r="A71" s="14">
+        <v>46322</v>
+      </c>
+      <c r="B71" s="15">
+        <v>300</v>
+      </c>
+      <c r="C71" s="15">
+        <v>20</v>
+      </c>
+      <c r="D71" s="15">
+        <v>120</v>
+      </c>
+      <c r="E71" s="15">
+        <v>60</v>
+      </c>
+      <c r="F71" s="15">
+        <v>350</v>
+      </c>
+      <c r="G71" s="15">
+        <v>7</v>
+      </c>
+      <c r="H71" s="15">
+        <v>150</v>
+      </c>
+      <c r="I71" s="16">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="J71" s="16">
+        <f t="shared" si="3"/>
+        <v>440</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N71" s="18" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="72" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9751A9E-942E-4741-9AD3-ECCD3F27CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEC9CEB-FD51-444D-BEDC-CC83CCDF8756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>assignment c++</t>
+  </si>
+  <si>
+    <t>today I study in python</t>
   </si>
 </sst>
 </file>
@@ -5129,26 +5132,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="14"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
-      <c r="N72" s="18"/>
+      <c r="A72" s="14">
+        <v>46323</v>
+      </c>
+      <c r="B72" s="15">
+        <v>300</v>
+      </c>
+      <c r="C72" s="15">
+        <v>10</v>
+      </c>
+      <c r="D72" s="15">
+        <v>120</v>
+      </c>
+      <c r="E72" s="15">
+        <v>50</v>
+      </c>
+      <c r="F72" s="15">
+        <v>300</v>
+      </c>
+      <c r="G72" s="15">
+        <v>6</v>
+      </c>
+      <c r="H72" s="15">
+        <v>170</v>
+      </c>
+      <c r="I72" s="16">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="J72" s="16">
+        <f t="shared" si="3"/>
+        <v>490</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L72" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M72" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N72" s="18" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="73" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="14"/>

--- a/12602441.xlsx
+++ b/12602441.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEC9CEB-FD51-444D-BEDC-CC83CCDF8756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED662462-4513-4C20-BA6B-1E083A937C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>today I study in python</t>
+  </si>
+  <si>
+    <t>today I do not study</t>
   </si>
 </sst>
 </file>
@@ -5178,48 +5181,96 @@
       </c>
     </row>
     <row r="73" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="14"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
-      <c r="I73" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
-      <c r="M73" s="17"/>
-      <c r="N73" s="18"/>
+      <c r="A73" s="14">
+        <v>46324</v>
+      </c>
+      <c r="B73" s="15">
+        <v>300</v>
+      </c>
+      <c r="C73" s="15">
+        <v>0</v>
+      </c>
+      <c r="D73" s="15">
+        <v>120</v>
+      </c>
+      <c r="E73" s="15">
+        <v>100</v>
+      </c>
+      <c r="F73" s="15">
+        <v>150</v>
+      </c>
+      <c r="G73" s="15">
+        <v>3</v>
+      </c>
+      <c r="H73" s="15">
+        <v>180</v>
+      </c>
+      <c r="I73" s="16">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+      <c r="J73" s="16">
+        <f t="shared" si="3"/>
+        <v>590</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L73" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N73" s="18" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="74" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="14"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-      <c r="M74" s="17"/>
-      <c r="N74" s="18"/>
+      <c r="A74" s="14">
+        <v>46325</v>
+      </c>
+      <c r="B74" s="15">
+        <v>300</v>
+      </c>
+      <c r="C74" s="15">
+        <v>0</v>
+      </c>
+      <c r="D74" s="15">
+        <v>60</v>
+      </c>
+      <c r="E74" s="15">
+        <v>60</v>
+      </c>
+      <c r="F74" s="15">
+        <v>250</v>
+      </c>
+      <c r="G74" s="15">
+        <v>5</v>
+      </c>
+      <c r="H74" s="15">
+        <v>150</v>
+      </c>
+      <c r="I74" s="16">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J74" s="16">
+        <f t="shared" si="3"/>
+        <v>620</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M74" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N74" s="18" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="75" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14"/>
